--- a/data/SCT-datas.xlsx
+++ b/data/SCT-datas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S54"/>
+  <dimension ref="A1:S135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,7 +528,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SCT-01</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>700000</v>
+        <v>960000</v>
       </c>
       <c r="E2" t="n">
         <v>0.0003</v>
@@ -563,37 +563,37 @@
         <v>0.95</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.06776867249448384</v>
+        <v>-0.09538517422818889</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.2557666599750519</v>
+        <v>-0.3347636461257935</v>
       </c>
       <c r="M2" t="n">
-        <v>819.1498474121094</v>
+        <v>808.7885306676229</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0163164627738297</v>
+        <v>0.01690574640154161</v>
       </c>
       <c r="O2" t="n">
-        <v>0.002518054387110169</v>
+        <v>0.003068959975445812</v>
       </c>
       <c r="P2" t="n">
-        <v>3.206759187153407</v>
+        <v>3.214562575022379</v>
       </c>
       <c r="Q2" t="n">
-        <v>1201.292449466766</v>
+        <v>1195.847212868175</v>
       </c>
       <c r="R2" t="n">
-        <v>5710.432734489441</v>
+        <v>13467.23175907135</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.186751961636458e-05</v>
+        <v>-7.082760283228859e-06</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SCT-02</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1600000</v>
+        <v>640000</v>
       </c>
       <c r="E3" t="n">
         <v>0.0003</v>
@@ -616,7 +616,7 @@
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>2048</v>
+        <v>4096</v>
       </c>
       <c r="H3" t="n">
         <v>20480</v>
@@ -628,37 +628,37 @@
         <v>0.95</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.05126657375367358</v>
+        <v>-0.07615977930254303</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08283635973930359</v>
+        <v>0.09836667031049728</v>
       </c>
       <c r="M3" t="n">
-        <v>895.9948001861572</v>
+        <v>861.9141731262207</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01711952688826902</v>
+        <v>0.01187793056255785</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001448348592495256</v>
+        <v>0.002142957818783731</v>
       </c>
       <c r="P3" t="n">
-        <v>3.162915460765362</v>
+        <v>3.225618503987789</v>
       </c>
       <c r="Q3" t="n">
-        <v>1201.777315306432</v>
+        <v>1202.52367259838</v>
       </c>
       <c r="R3" t="n">
-        <v>20568.13388299942</v>
+        <v>9154.910551309586</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.49252431189433e-06</v>
+        <v>-8.319008566571803e-06</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SCT-03</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -672,10 +672,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1590000</v>
+        <v>420000</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0003</v>
+        <v>0.001</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
@@ -693,37 +693,37 @@
         <v>0.95</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.04648391508453642</v>
+        <v>-0.03583470593358195</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>910.2154644012451</v>
+        <v>940.1122947515444</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01687522647852028</v>
+        <v>0.01660997136250923</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001304589455418796</v>
+        <v>0.003079225850151009</v>
       </c>
       <c r="P4" t="n">
-        <v>3.179975602030754</v>
+        <v>3.18493793731512</v>
       </c>
       <c r="Q4" t="n">
-        <v>1195.769820999313</v>
+        <v>1197.630839029948</v>
       </c>
       <c r="R4" t="n">
-        <v>20635.65886068344</v>
+        <v>27806.82258176804</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.252601450642362e-06</v>
+        <v>-1.288701930190238e-06</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SCT-04</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -737,10 +737,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1600000</v>
+        <v>430000</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0003</v>
+        <v>0.001</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
@@ -758,37 +758,37 @@
         <v>0.95</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.06504995698824131</v>
+        <v>-0.03331878452106964</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.02931110933423042</v>
+        <v>0.1563999950885773</v>
       </c>
       <c r="M5" t="n">
-        <v>745.9085684776306</v>
+        <v>894.7310350994732</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01686630337188641</v>
+        <v>0.01652241238441907</v>
       </c>
       <c r="O5" t="n">
-        <v>0.004394545304239728</v>
+        <v>0.005118600018441181</v>
       </c>
       <c r="P5" t="n">
-        <v>3.170086568593979</v>
+        <v>3.193836467210637</v>
       </c>
       <c r="Q5" t="n">
-        <v>1212.315616529815</v>
+        <v>1197.617244175502</v>
       </c>
       <c r="R5" t="n">
-        <v>20644.58687090874</v>
+        <v>27800.90120983124</v>
       </c>
       <c r="S5" t="n">
-        <v>-3.150944961747153e-06</v>
+        <v>-1.198478576992573e-06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SCT-05</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -802,10 +802,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>850000</v>
+        <v>430000</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003</v>
+        <v>0.001</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -823,37 +823,37 @@
         <v>0.95</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.08545626429293085</v>
+        <v>-0.04652095295835373</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1544727236032486</v>
+        <v>-0.1818181872367859</v>
       </c>
       <c r="M6" t="n">
-        <v>867.0976217830882</v>
+        <v>822.2990410383358</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01616493837000468</v>
+        <v>0.01614896743558347</v>
       </c>
       <c r="O6" t="n">
-        <v>0.00191553914079962</v>
+        <v>0.004425249790074304</v>
       </c>
       <c r="P6" t="n">
-        <v>3.222252974790685</v>
+        <v>3.205345713815024</v>
       </c>
       <c r="Q6" t="n">
-        <v>1197.116728911529</v>
+        <v>1201.294261443309</v>
       </c>
       <c r="R6" t="n">
-        <v>9006.747295379639</v>
+        <v>27792.19750285149</v>
       </c>
       <c r="S6" t="n">
-        <v>-9.488027307790567e-06</v>
+        <v>-1.673885375691529e-06</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SCT-06</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -867,10 +867,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1620000</v>
+        <v>430000</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0003</v>
+        <v>0.001</v>
       </c>
       <c r="F7" t="n">
         <v>3</v>
@@ -888,37 +888,37 @@
         <v>0.95</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.03488386088219454</v>
+        <v>-0.09217834647008499</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.07896000146865845</v>
       </c>
       <c r="M7" t="n">
-        <v>957.1199520555742</v>
+        <v>803.0100282181141</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01660817282895247</v>
+        <v>0.01678411923348904</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0006292404498197375</v>
+        <v>0.006974894469385618</v>
       </c>
       <c r="P7" t="n">
-        <v>3.089862684530714</v>
+        <v>3.198370922443479</v>
       </c>
       <c r="Q7" t="n">
-        <v>1200.518920898438</v>
+        <v>1193.853396767064</v>
       </c>
       <c r="R7" t="n">
-        <v>17361.37713456154</v>
+        <v>27786.51607084274</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.009279598722082e-06</v>
+        <v>-3.317376897307778e-06</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SCT-07</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1630000</v>
+        <v>430000</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0003</v>
+        <v>0.001</v>
       </c>
       <c r="F8" t="n">
         <v>3</v>
@@ -953,37 +953,37 @@
         <v>0.95</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.05568106853591701</v>
+        <v>-0.1129011954505776</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2000666558742523</v>
+        <v>-0.107626661658287</v>
       </c>
       <c r="M8" t="n">
-        <v>902.4359194515673</v>
+        <v>721.2506571924964</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0169349475329121</v>
+        <v>0.01599185178056359</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001417398604623941</v>
+        <v>0.007707594343810342</v>
       </c>
       <c r="P8" t="n">
-        <v>3.194538844875031</v>
+        <v>3.18030551422474</v>
       </c>
       <c r="Q8" t="n">
-        <v>1197.364702273638</v>
+        <v>1194.321503429878</v>
       </c>
       <c r="R8" t="n">
-        <v>17348.95117688179</v>
+        <v>27780.84646821022</v>
       </c>
       <c r="S8" t="n">
-        <v>-3.20947750490614e-06</v>
+        <v>-4.063994075190297e-06</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SCT-08</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1800000</v>
+        <v>950000</v>
       </c>
       <c r="E9" t="n">
         <v>0.0003</v>
@@ -1018,37 +1018,37 @@
         <v>0.95</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.007203004727812691</v>
+        <v>-0.07055388631691274</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.06188484653830528</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>395.0989760504829</v>
+        <v>809.2034902472245</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01664375866598943</v>
+        <v>0.01653701509349048</v>
       </c>
       <c r="O9" t="n">
-        <v>0.03541058359110406</v>
+        <v>0.002752947615445836</v>
       </c>
       <c r="P9" t="n">
-        <v>2.970535337924957</v>
+        <v>3.198949211522153</v>
       </c>
       <c r="Q9" t="n">
-        <v>1266.412002208621</v>
+        <v>1200.000078573994</v>
       </c>
       <c r="R9" t="n">
-        <v>16574.29940724373</v>
+        <v>13398.03617310524</v>
       </c>
       <c r="S9" t="n">
-        <v>-4.345887902003657e-07</v>
+        <v>-5.265987149560038e-06</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SCT-10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1062,7 +1062,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1590000</v>
+        <v>940000</v>
       </c>
       <c r="E10" t="n">
         <v>0.0003</v>
@@ -1083,37 +1083,37 @@
         <v>0.95</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.006587811028174822</v>
+        <v>-0.07143435520219042</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05015329271554947</v>
+        <v>-0.00800000037997961</v>
       </c>
       <c r="M10" t="n">
-        <v>526.1577834363254</v>
+        <v>537.2697325361536</v>
       </c>
       <c r="N10" t="n">
-        <v>0.01700007033844789</v>
+        <v>0.01705224896696481</v>
       </c>
       <c r="O10" t="n">
-        <v>0.02174308401687692</v>
+        <v>0.01243311499869874</v>
       </c>
       <c r="P10" t="n">
-        <v>3.102992681587267</v>
+        <v>3.178954466860345</v>
       </c>
       <c r="Q10" t="n">
-        <v>1247.458277695844</v>
+        <v>1202.710443911345</v>
       </c>
       <c r="R10" t="n">
-        <v>17719.96104216576</v>
+        <v>13369.20175242424</v>
       </c>
       <c r="S10" t="n">
-        <v>-3.71773448739459e-07</v>
+        <v>-5.343202722573711e-06</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SCT-11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1580000</v>
+        <v>940000</v>
       </c>
       <c r="E11" t="n">
         <v>0.0003</v>
@@ -1148,37 +1148,37 @@
         <v>0.95</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.06061652164789848</v>
+        <v>-0.06833108481108904</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>933.1438983917236</v>
+        <v>853.3214104835023</v>
       </c>
       <c r="N11" t="n">
-        <v>0.01637726944141291</v>
+        <v>0.01679611158405625</v>
       </c>
       <c r="O11" t="n">
-        <v>0.001073434002266269</v>
+        <v>0.002057156911347235</v>
       </c>
       <c r="P11" t="n">
-        <v>3.177250443398953</v>
+        <v>3.204072726533768</v>
       </c>
       <c r="Q11" t="n">
-        <v>1190.790929885138</v>
+        <v>1200.800971137153</v>
       </c>
       <c r="R11" t="n">
-        <v>17706.06028580666</v>
+        <v>13338.27844715118</v>
       </c>
       <c r="S11" t="n">
-        <v>-3.423490074553132e-06</v>
+        <v>-5.122931349936193e-06</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SCT-12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1192,7 +1192,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>670000</v>
+        <v>940000</v>
       </c>
       <c r="E12" t="n">
         <v>0.0003</v>
@@ -1213,37 +1213,37 @@
         <v>0.95</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.04847010820145335</v>
+        <v>-0.05638179661052183</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="M12" t="n">
-        <v>844.8394438799689</v>
+        <v>817.9299160571809</v>
       </c>
       <c r="N12" t="n">
-        <v>0.01680771180338437</v>
+        <v>0.01673840527790924</v>
       </c>
       <c r="O12" t="n">
-        <v>0.002063998573351367</v>
+        <v>0.002504978534742868</v>
       </c>
       <c r="P12" t="n">
-        <v>3.206857951248393</v>
+        <v>3.199009930833857</v>
       </c>
       <c r="Q12" t="n">
-        <v>1216.972176688058</v>
+        <v>1199.497548173114</v>
       </c>
       <c r="R12" t="n">
-        <v>7134.861765623093</v>
+        <v>13318.77669405937</v>
       </c>
       <c r="S12" t="n">
-        <v>-6.793419381296229e-06</v>
+        <v>-4.233256394761091e-06</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SCT-13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>660000</v>
+        <v>640000</v>
       </c>
       <c r="E13" t="n">
         <v>0.0003</v>
@@ -1266,7 +1266,7 @@
         <v>3</v>
       </c>
       <c r="G13" t="n">
-        <v>2048</v>
+        <v>4096</v>
       </c>
       <c r="H13" t="n">
         <v>20480</v>
@@ -1278,37 +1278,37 @@
         <v>0.95</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.06874313938212306</v>
+        <v>-0.05627055839431705</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>0.1137090921401978</v>
       </c>
       <c r="M13" t="n">
-        <v>870.3296392104205</v>
+        <v>852.0066032409668</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0175879750280611</v>
+        <v>0.01094359968756807</v>
       </c>
       <c r="O13" t="n">
-        <v>0.001804821685694943</v>
+        <v>0.002164138281182988</v>
       </c>
       <c r="P13" t="n">
-        <v>3.208549730917987</v>
+        <v>3.22988998144865</v>
       </c>
       <c r="Q13" t="n">
-        <v>1193.827049842248</v>
+        <v>1208.422500084186</v>
       </c>
       <c r="R13" t="n">
-        <v>7082.208986520767</v>
+        <v>9181.32715511322</v>
       </c>
       <c r="S13" t="n">
-        <v>-9.706454513409394e-06</v>
+        <v>-6.128804413965265e-06</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SCT-14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1322,7 +1322,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>970000</v>
+        <v>640000</v>
       </c>
       <c r="E14" t="n">
         <v>0.0003</v>
@@ -1331,7 +1331,7 @@
         <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>2048</v>
+        <v>4096</v>
       </c>
       <c r="H14" t="n">
         <v>20480</v>
@@ -1343,37 +1343,37 @@
         <v>0.95</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.03169108930370319</v>
+        <v>-0.07813005110619997</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.1728499978780746</v>
+        <v>0.07581818103790283</v>
       </c>
       <c r="M14" t="n">
-        <v>511.6548633378806</v>
+        <v>903.0657186508179</v>
       </c>
       <c r="N14" t="n">
-        <v>0.01703262571245432</v>
+        <v>0.01115176502358297</v>
       </c>
       <c r="O14" t="n">
-        <v>0.01460505981805101</v>
+        <v>0.001540249476451647</v>
       </c>
       <c r="P14" t="n">
-        <v>3.142604343669931</v>
+        <v>3.22623385488987</v>
       </c>
       <c r="Q14" t="n">
-        <v>1211.005189286902</v>
+        <v>1204.601530113999</v>
       </c>
       <c r="R14" t="n">
-        <v>10351.53935980797</v>
+        <v>9174.959064483643</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.061485659490464e-06</v>
+        <v>-8.515574898709049e-06</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SCT-15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1370000</v>
+        <v>620000</v>
       </c>
       <c r="E15" t="n">
         <v>0.0003</v>
@@ -1396,7 +1396,7 @@
         <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>2048</v>
+        <v>4096</v>
       </c>
       <c r="H15" t="n">
         <v>20480</v>
@@ -1408,37 +1408,37 @@
         <v>0.95</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.01534736695330604</v>
+        <v>-0.07833573924347995</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.05311926454305649</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>421.8068810901503</v>
+        <v>868.4430648561508</v>
       </c>
       <c r="N15" t="n">
-        <v>0.01676924241473898</v>
+        <v>0.01156356831177555</v>
       </c>
       <c r="O15" t="n">
-        <v>0.01796575695516367</v>
+        <v>0.001920043454698191</v>
       </c>
       <c r="P15" t="n">
-        <v>3.071267639633513</v>
+        <v>3.24451808702378</v>
       </c>
       <c r="Q15" t="n">
-        <v>1241.230949797454</v>
+        <v>1197.347871003328</v>
       </c>
       <c r="R15" t="n">
-        <v>15316.47149729729</v>
+        <v>9167.662488460541</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.002017139261755e-06</v>
+        <v>-8.54478874435901e-06</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SCT-16</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1370000</v>
+        <v>640000</v>
       </c>
       <c r="E16" t="n">
         <v>0.0003</v>
@@ -1461,7 +1461,7 @@
         <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>2048</v>
+        <v>4096</v>
       </c>
       <c r="H16" t="n">
         <v>20480</v>
@@ -1473,37 +1473,37 @@
         <v>0.95</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.05886817818556837</v>
+        <v>-0.08588541919925774</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.06612307578325272</v>
+        <v>-0.001230767113156617</v>
       </c>
       <c r="M16" t="n">
-        <v>819.7258233954436</v>
+        <v>864.7513580322266</v>
       </c>
       <c r="N16" t="n">
-        <v>0.01705227925309113</v>
+        <v>0.01169851804473277</v>
       </c>
       <c r="O16" t="n">
-        <v>0.002442500140941341</v>
+        <v>0.002095760393723171</v>
       </c>
       <c r="P16" t="n">
-        <v>3.18314605733774</v>
+        <v>3.240418292582035</v>
       </c>
       <c r="Q16" t="n">
-        <v>1200.119413731462</v>
+        <v>1200.0670703125</v>
       </c>
       <c r="R16" t="n">
-        <v>15307.74420166016</v>
+        <v>9161.578250169754</v>
       </c>
       <c r="S16" t="n">
-        <v>-3.845646844502667e-06</v>
+        <v>-9.37452225523112e-06</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SCT-17</t>
+          <t>SCT-01</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1517,7 +1517,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1020000</v>
+        <v>700000</v>
       </c>
       <c r="E17" t="n">
         <v>0.0003</v>
@@ -1538,37 +1538,37 @@
         <v>0.95</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.01708121148084163</v>
+        <v>-0.06776867249448384</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.1704639941453934</v>
+        <v>-0.2557666599750519</v>
       </c>
       <c r="M17" t="n">
-        <v>843.7150795132507</v>
+        <v>819.1498474121094</v>
       </c>
       <c r="N17" t="n">
-        <v>0.01649789545843576</v>
+        <v>0.0163164627738297</v>
       </c>
       <c r="O17" t="n">
-        <v>0.002033265825135226</v>
+        <v>0.002518054387110169</v>
       </c>
       <c r="P17" t="n">
-        <v>3.197372551057853</v>
+        <v>3.206759187153407</v>
       </c>
       <c r="Q17" t="n">
-        <v>1209.330748758198</v>
+        <v>1201.292449466766</v>
       </c>
       <c r="R17" t="n">
-        <v>11573.14974069595</v>
+        <v>5710.432734489441</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.475934543625325e-06</v>
+        <v>-1.186751961636458e-05</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SCT-18</t>
+          <t>SCT-02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>510000</v>
+        <v>1600000</v>
       </c>
       <c r="E18" t="n">
         <v>0.0003</v>
@@ -1603,37 +1603,37 @@
         <v>0.95</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.05988184779005892</v>
+        <v>-0.05126657375367358</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.4166666567325592</v>
+        <v>0.08283635973930359</v>
       </c>
       <c r="M18" t="n">
-        <v>838.8257948931525</v>
+        <v>895.9948001861572</v>
       </c>
       <c r="N18" t="n">
-        <v>0.01747349929064512</v>
+        <v>0.01711952688826902</v>
       </c>
       <c r="O18" t="n">
-        <v>0.002268892072606832</v>
+        <v>0.001448348592495256</v>
       </c>
       <c r="P18" t="n">
-        <v>3.227826857099346</v>
+        <v>3.162915460765362</v>
       </c>
       <c r="Q18" t="n">
-        <v>1201.803751627604</v>
+        <v>1201.777315306432</v>
       </c>
       <c r="R18" t="n">
-        <v>8108.97464799881</v>
+        <v>20568.13388299942</v>
       </c>
       <c r="S18" t="n">
-        <v>-7.384638673748596e-06</v>
+        <v>-2.49252431189433e-06</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SCT-19</t>
+          <t>SCT-03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>510000</v>
+        <v>1590000</v>
       </c>
       <c r="E19" t="n">
         <v>0.0003</v>
@@ -1668,37 +1668,37 @@
         <v>0.95</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.0690705474293745</v>
+        <v>-0.04648391508453642</v>
       </c>
       <c r="L19" t="n">
-        <v>0.04608000069856644</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>828.3960690965839</v>
+        <v>910.2154644012451</v>
       </c>
       <c r="N19" t="n">
-        <v>0.01688212221083434</v>
+        <v>0.01687522647852028</v>
       </c>
       <c r="O19" t="n">
-        <v>0.00247366292371779</v>
+        <v>0.001304589455418796</v>
       </c>
       <c r="P19" t="n">
-        <v>3.233933864855299</v>
+        <v>3.179975602030754</v>
       </c>
       <c r="Q19" t="n">
-        <v>1203.561820652174</v>
+        <v>1195.769820999313</v>
       </c>
       <c r="R19" t="n">
-        <v>8104.788193702698</v>
+        <v>20635.65886068344</v>
       </c>
       <c r="S19" t="n">
-        <v>-8.522190312516904e-06</v>
+        <v>-2.252601450642362e-06</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SCT-20</t>
+          <t>SCT-04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>510000</v>
+        <v>1600000</v>
       </c>
       <c r="E20" t="n">
         <v>0.0003</v>
@@ -1733,37 +1733,37 @@
         <v>0.95</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.09828426047027403</v>
+        <v>-0.06504995698824131</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.1666666716337204</v>
+        <v>-0.02931110933423042</v>
       </c>
       <c r="M20" t="n">
-        <v>882.9021965475644</v>
+        <v>745.9085684776306</v>
       </c>
       <c r="N20" t="n">
-        <v>0.01686818039287692</v>
+        <v>0.01686630337188641</v>
       </c>
       <c r="O20" t="n">
-        <v>0.001900745525290404</v>
+        <v>0.004394545304239728</v>
       </c>
       <c r="P20" t="n">
-        <v>3.232472214044309</v>
+        <v>3.170086568593979</v>
       </c>
       <c r="Q20" t="n">
-        <v>1198.646314119038</v>
+        <v>1212.315616529815</v>
       </c>
       <c r="R20" t="n">
-        <v>8100.919000387192</v>
+        <v>20644.58687090874</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.213248280418264e-05</v>
+        <v>-3.150944961747153e-06</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SCT-21</t>
+          <t>SCT-05</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1777,7 +1777,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1300000</v>
+        <v>850000</v>
       </c>
       <c r="E21" t="n">
         <v>0.0003</v>
@@ -1798,37 +1798,37 @@
         <v>0.95</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.07821390980803139</v>
+        <v>-0.08545626429293085</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.3636363744735718</v>
+        <v>0.1544727236032486</v>
       </c>
       <c r="M21" t="n">
-        <v>883.3144681490385</v>
+        <v>867.0976217830882</v>
       </c>
       <c r="N21" t="n">
-        <v>0.01725451249318818</v>
+        <v>0.01616493837000468</v>
       </c>
       <c r="O21" t="n">
-        <v>0.001746478429928781</v>
+        <v>0.00191553914079962</v>
       </c>
       <c r="P21" t="n">
-        <v>3.202359318733215</v>
+        <v>3.222252974790685</v>
       </c>
       <c r="Q21" t="n">
-        <v>1189.500042854471</v>
+        <v>1197.116728911529</v>
       </c>
       <c r="R21" t="n">
-        <v>14756.54293203354</v>
+        <v>9006.747295379639</v>
       </c>
       <c r="S21" t="n">
-        <v>-5.300286806216953e-06</v>
+        <v>-9.488027307790567e-06</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SCT-22</t>
+          <t>SCT-06</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1290000</v>
+        <v>1620000</v>
       </c>
       <c r="E22" t="n">
         <v>0.0003</v>
@@ -1863,37 +1863,37 @@
         <v>0.95</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.04709835156307433</v>
+        <v>-0.03488386088219454</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.3333333432674408</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>927.1865910966267</v>
+        <v>957.1199520555742</v>
       </c>
       <c r="N22" t="n">
-        <v>0.01703438789473247</v>
+        <v>0.01660817282895247</v>
       </c>
       <c r="O22" t="n">
-        <v>0.00102745947567843</v>
+        <v>0.0006292404498197375</v>
       </c>
       <c r="P22" t="n">
-        <v>3.203014880187752</v>
+        <v>3.089862684530714</v>
       </c>
       <c r="Q22" t="n">
-        <v>1202.510055763134</v>
+        <v>1200.518920898438</v>
       </c>
       <c r="R22" t="n">
-        <v>14736.30408143997</v>
+        <v>17361.37713456154</v>
       </c>
       <c r="S22" t="n">
-        <v>-3.196076255130592e-06</v>
+        <v>-2.009279598722082e-06</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SCT-23</t>
+          <t>SCT-07</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1907,7 +1907,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1290000</v>
+        <v>1630000</v>
       </c>
       <c r="E23" t="n">
         <v>0.0003</v>
@@ -1928,37 +1928,37 @@
         <v>0.95</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.06172820547227423</v>
+        <v>-0.05568106853591701</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.02329999580979347</v>
+        <v>0.2000666558742523</v>
       </c>
       <c r="M23" t="n">
-        <v>872.4737350109011</v>
+        <v>902.4359194515673</v>
       </c>
       <c r="N23" t="n">
-        <v>0.01681118815516432</v>
+        <v>0.0169349475329121</v>
       </c>
       <c r="O23" t="n">
-        <v>0.001759909112214094</v>
+        <v>0.001417398604623941</v>
       </c>
       <c r="P23" t="n">
-        <v>3.188865291979886</v>
+        <v>3.194538844875031</v>
       </c>
       <c r="Q23" t="n">
-        <v>1197.716013382892</v>
+        <v>1197.364702273638</v>
       </c>
       <c r="R23" t="n">
-        <v>14722.9565551281</v>
+        <v>17348.95117688179</v>
       </c>
       <c r="S23" t="n">
-        <v>-4.192650113524509e-06</v>
+        <v>-3.20947750490614e-06</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SCT-24</t>
+          <t>SCT-08</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>620000</v>
+        <v>1800000</v>
       </c>
       <c r="E24" t="n">
         <v>0.0003</v>
@@ -1993,37 +1993,37 @@
         <v>0.95</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.08076840271279516</v>
+        <v>-0.007203004727812691</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1558909118175507</v>
+        <v>-0.06188484653830528</v>
       </c>
       <c r="M24" t="n">
-        <v>809.3843196745842</v>
+        <v>395.0989760504829</v>
       </c>
       <c r="N24" t="n">
-        <v>0.01709947157008895</v>
+        <v>0.01664375866598943</v>
       </c>
       <c r="O24" t="n">
-        <v>0.002677177145258234</v>
+        <v>0.03541058359110406</v>
       </c>
       <c r="P24" t="n">
-        <v>3.213665427700166</v>
+        <v>2.970535337924957</v>
       </c>
       <c r="Q24" t="n">
-        <v>1196.785132271903</v>
+        <v>1266.412002208621</v>
       </c>
       <c r="R24" t="n">
-        <v>9304.627391815186</v>
+        <v>16574.29940724373</v>
       </c>
       <c r="S24" t="n">
-        <v>-8.680455359646435e-06</v>
+        <v>-4.345887902003657e-07</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SCT-25</t>
+          <t>SCT-10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>620000</v>
+        <v>1590000</v>
       </c>
       <c r="E25" t="n">
         <v>0.0003</v>
@@ -2058,37 +2058,37 @@
         <v>0.95</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.06089504700784962</v>
+        <v>-0.006587811028174822</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.1562909036874771</v>
+        <v>0.05015329271554947</v>
       </c>
       <c r="M25" t="n">
-        <v>850.7828113186744</v>
+        <v>526.1577834363254</v>
       </c>
       <c r="N25" t="n">
-        <v>0.0173359208515492</v>
+        <v>0.01700007033844789</v>
       </c>
       <c r="O25" t="n">
-        <v>0.00212054752820881</v>
+        <v>0.02174308401687692</v>
       </c>
       <c r="P25" t="n">
-        <v>3.223078893076989</v>
+        <v>3.102992681587267</v>
       </c>
       <c r="Q25" t="n">
-        <v>1200.468372051532</v>
+        <v>1247.458277695844</v>
       </c>
       <c r="R25" t="n">
-        <v>9284.246625423431</v>
+        <v>17719.96104216576</v>
       </c>
       <c r="S25" t="n">
-        <v>-6.558964821237969e-06</v>
+        <v>-3.71773448739459e-07</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SCT-26</t>
+          <t>SCT-11</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>620000</v>
+        <v>1580000</v>
       </c>
       <c r="E26" t="n">
         <v>0.0003</v>
@@ -2123,37 +2123,37 @@
         <v>0.95</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.08695605206077979</v>
+        <v>-0.06061652164789848</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.4781684279441833</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>778.2292283581149</v>
+        <v>933.1438983917236</v>
       </c>
       <c r="N26" t="n">
-        <v>0.01692195176812155</v>
+        <v>0.01637726944141291</v>
       </c>
       <c r="O26" t="n">
-        <v>0.003309059979593648</v>
+        <v>0.001073434002266269</v>
       </c>
       <c r="P26" t="n">
-        <v>3.207571560336698</v>
+        <v>3.177250443398953</v>
       </c>
       <c r="Q26" t="n">
-        <v>1197.860078456038</v>
+        <v>1190.790929885138</v>
       </c>
       <c r="R26" t="n">
-        <v>9270.770953893661</v>
+        <v>17706.06028580666</v>
       </c>
       <c r="S26" t="n">
-        <v>-9.379592322282413e-06</v>
+        <v>-3.423490074553132e-06</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SCT-27</t>
+          <t>SCT-12</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1480000</v>
+        <v>670000</v>
       </c>
       <c r="E27" t="n">
         <v>0.0003</v>
@@ -2188,37 +2188,37 @@
         <v>0.95</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.03887055685422761</v>
+        <v>-0.04847010820145335</v>
       </c>
       <c r="L27" t="n">
-        <v>0.04770307615399361</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>466.1728206840721</v>
+        <v>844.8394438799689</v>
       </c>
       <c r="N27" t="n">
-        <v>0.01646833285095467</v>
+        <v>0.01680771180338437</v>
       </c>
       <c r="O27" t="n">
-        <v>0.01808865653668139</v>
+        <v>0.002063998573351367</v>
       </c>
       <c r="P27" t="n">
-        <v>3.096878704187032</v>
+        <v>3.206857951248393</v>
       </c>
       <c r="Q27" t="n">
-        <v>1241.916709586366</v>
+        <v>1216.972176688058</v>
       </c>
       <c r="R27" t="n">
-        <v>20326.9064142704</v>
+        <v>7134.861765623093</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.912271157353228e-06</v>
+        <v>-6.793419381296229e-06</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SCT-28</t>
+          <t>SCT-13</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>950000</v>
+        <v>660000</v>
       </c>
       <c r="E28" t="n">
         <v>0.0003</v>
@@ -2253,37 +2253,37 @@
         <v>0.95</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.02410208596379165</v>
+        <v>-0.06874313938212306</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>952.9241615653838</v>
+        <v>870.3296392104205</v>
       </c>
       <c r="N28" t="n">
-        <v>0.01708082157625433</v>
+        <v>0.0175879750280611</v>
       </c>
       <c r="O28" t="n">
-        <v>0.000636368792025561</v>
+        <v>0.001804821685694943</v>
       </c>
       <c r="P28" t="n">
-        <v>3.043231468072674</v>
+        <v>3.208549730917987</v>
       </c>
       <c r="Q28" t="n">
-        <v>1202.217054887251</v>
+        <v>1193.827049842248</v>
       </c>
       <c r="R28" t="n">
-        <v>20324.13341164589</v>
+        <v>7082.208986520767</v>
       </c>
       <c r="S28" t="n">
-        <v>-1.185885049838384e-06</v>
+        <v>-9.706454513409394e-06</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SCT-29</t>
+          <t>SCT-14</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1490000</v>
+        <v>970000</v>
       </c>
       <c r="E29" t="n">
         <v>0.0003</v>
@@ -2318,37 +2318,37 @@
         <v>0.95</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.0625108793399753</v>
+        <v>-0.03169108930370319</v>
       </c>
       <c r="L29" t="n">
-        <v>0.04741666465997696</v>
+        <v>-0.1728499978780746</v>
       </c>
       <c r="M29" t="n">
-        <v>800.0971218851589</v>
+        <v>511.6548633378806</v>
       </c>
       <c r="N29" t="n">
-        <v>0.01720528434152188</v>
+        <v>0.01703262571245432</v>
       </c>
       <c r="O29" t="n">
-        <v>0.003114550544220644</v>
+        <v>0.01460505981805101</v>
       </c>
       <c r="P29" t="n">
-        <v>3.174362001803097</v>
+        <v>3.142604343669931</v>
       </c>
       <c r="Q29" t="n">
-        <v>1209.78265953064</v>
+        <v>1211.005189286902</v>
       </c>
       <c r="R29" t="n">
-        <v>20324.03649783134</v>
+        <v>10351.53935980797</v>
       </c>
       <c r="S29" t="n">
-        <v>-3.075711822631565e-06</v>
+        <v>-3.061485659490464e-06</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SCT-30</t>
+          <t>SCT-15</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2362,7 +2362,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>770000</v>
+        <v>1370000</v>
       </c>
       <c r="E30" t="n">
         <v>0.0003</v>
@@ -2383,37 +2383,37 @@
         <v>0.95</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.05482129686868858</v>
+        <v>-0.01534736695330604</v>
       </c>
       <c r="L30" t="n">
-        <v>0.1436000019311905</v>
+        <v>-0.05311926454305649</v>
       </c>
       <c r="M30" t="n">
-        <v>884.974719555347</v>
+        <v>421.8068810901503</v>
       </c>
       <c r="N30" t="n">
-        <v>0.01615734424974237</v>
+        <v>0.01676924241473898</v>
       </c>
       <c r="O30" t="n">
-        <v>0.001539779463044916</v>
+        <v>0.01796575695516367</v>
       </c>
       <c r="P30" t="n">
-        <v>3.204005222815972</v>
+        <v>3.071267639633513</v>
       </c>
       <c r="Q30" t="n">
-        <v>1193.449300797259</v>
+        <v>1241.230949797454</v>
       </c>
       <c r="R30" t="n">
-        <v>9646.979743719101</v>
+        <v>15316.47149729729</v>
       </c>
       <c r="S30" t="n">
-        <v>-5.682741990246358e-06</v>
+        <v>-1.002017139261755e-06</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SCT-31</t>
+          <t>SCT-16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>760000</v>
+        <v>1370000</v>
       </c>
       <c r="E31" t="n">
         <v>0.0003</v>
@@ -2448,37 +2448,37 @@
         <v>0.95</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.03643133456353098</v>
+        <v>-0.05886817818556837</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.04510000348091125</v>
+        <v>-0.06612307578325272</v>
       </c>
       <c r="M31" t="n">
-        <v>838.6874678762335</v>
+        <v>819.7258233954436</v>
       </c>
       <c r="N31" t="n">
-        <v>0.01671373338571617</v>
+        <v>0.01705227925309113</v>
       </c>
       <c r="O31" t="n">
-        <v>0.002221554686314318</v>
+        <v>0.002442500140941341</v>
       </c>
       <c r="P31" t="n">
-        <v>3.221089316041846</v>
+        <v>3.18314605733774</v>
       </c>
       <c r="Q31" t="n">
-        <v>1202.740619962178</v>
+        <v>1200.119413731462</v>
       </c>
       <c r="R31" t="n">
-        <v>9625.807464122772</v>
+        <v>15307.74420166016</v>
       </c>
       <c r="S31" t="n">
-        <v>-3.784756208693924e-06</v>
+        <v>-3.845646844502667e-06</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SCT-32</t>
+          <t>SCT-17</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2492,7 +2492,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>770000</v>
+        <v>1020000</v>
       </c>
       <c r="E32" t="n">
         <v>0.0003</v>
@@ -2513,37 +2513,37 @@
         <v>0.95</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.06088397360418911</v>
+        <v>-0.01708121148084163</v>
       </c>
       <c r="L32" t="n">
-        <v>0.03985454514622688</v>
+        <v>-0.1704639941453934</v>
       </c>
       <c r="M32" t="n">
-        <v>853.4246199967025</v>
+        <v>843.7150795132507</v>
       </c>
       <c r="N32" t="n">
-        <v>0.0168667607275503</v>
+        <v>0.01649789545843576</v>
       </c>
       <c r="O32" t="n">
-        <v>0.002109424436431644</v>
+        <v>0.002033265825135226</v>
       </c>
       <c r="P32" t="n">
-        <v>3.21989875954467</v>
+        <v>3.197372551057853</v>
       </c>
       <c r="Q32" t="n">
-        <v>1199.984812266791</v>
+        <v>1209.330748758198</v>
       </c>
       <c r="R32" t="n">
-        <v>9614.763172388077</v>
+        <v>11573.14974069595</v>
       </c>
       <c r="S32" t="n">
-        <v>-6.332342514586034e-06</v>
+        <v>-1.475934543625325e-06</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SCT-33</t>
+          <t>SCT-18</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2557,7 +2557,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1590000</v>
+        <v>510000</v>
       </c>
       <c r="E33" t="n">
         <v>0.0003</v>
@@ -2578,37 +2578,37 @@
         <v>0.95</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.04188887321144202</v>
+        <v>-0.05988184779005892</v>
       </c>
       <c r="L33" t="n">
-        <v>0.3271910548210144</v>
+        <v>-0.4166666567325592</v>
       </c>
       <c r="M33" t="n">
-        <v>726.0532055740837</v>
+        <v>838.8257948931525</v>
       </c>
       <c r="N33" t="n">
-        <v>0.01691138584519157</v>
+        <v>0.01747349929064512</v>
       </c>
       <c r="O33" t="n">
-        <v>0.006647793710059788</v>
+        <v>0.002268892072606832</v>
       </c>
       <c r="P33" t="n">
-        <v>3.142067582352357</v>
+        <v>3.227826857099346</v>
       </c>
       <c r="Q33" t="n">
-        <v>1214.107131465789</v>
+        <v>1201.803751627604</v>
       </c>
       <c r="R33" t="n">
-        <v>15146.50751519203</v>
+        <v>8108.97464799881</v>
       </c>
       <c r="S33" t="n">
-        <v>-2.76557966709007e-06</v>
+        <v>-7.384638673748596e-06</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SCT-34</t>
+          <t>SCT-19</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2622,7 +2622,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>730000</v>
+        <v>510000</v>
       </c>
       <c r="E34" t="n">
         <v>0.0003</v>
@@ -2643,37 +2643,37 @@
         <v>0.95</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.0632665089398546</v>
+        <v>-0.0690705474293745</v>
       </c>
       <c r="L34" t="n">
-        <v>0.4811508655548096</v>
+        <v>0.04608000069856644</v>
       </c>
       <c r="M34" t="n">
-        <v>583.2877704150056</v>
+        <v>828.3960690965839</v>
       </c>
       <c r="N34" t="n">
-        <v>0.01691351620042149</v>
+        <v>0.01688212221083434</v>
       </c>
       <c r="O34" t="n">
-        <v>0.008947532817461145</v>
+        <v>0.00247366292371779</v>
       </c>
       <c r="P34" t="n">
-        <v>3.175101247552323</v>
+        <v>3.233933864855299</v>
       </c>
       <c r="Q34" t="n">
-        <v>1210.351660834418</v>
+        <v>1203.561820652174</v>
       </c>
       <c r="R34" t="n">
-        <v>10138.08539009094</v>
+        <v>8104.788193702698</v>
       </c>
       <c r="S34" t="n">
-        <v>-6.240478996329214e-06</v>
+        <v>-8.522190312516904e-06</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SCT-35</t>
+          <t>SCT-20</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>730000</v>
+        <v>510000</v>
       </c>
       <c r="E35" t="n">
         <v>0.0003</v>
@@ -2708,37 +2708,37 @@
         <v>0.95</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.08329656442040451</v>
+        <v>-0.09828426047027403</v>
       </c>
       <c r="L35" t="n">
-        <v>0.005119999870657921</v>
+        <v>-0.1666666716337204</v>
       </c>
       <c r="M35" t="n">
-        <v>908.7330548012093</v>
+        <v>882.9021965475644</v>
       </c>
       <c r="N35" t="n">
-        <v>0.01671572432250661</v>
+        <v>0.01686818039287692</v>
       </c>
       <c r="O35" t="n">
-        <v>0.001475003170686678</v>
+        <v>0.001900745525290404</v>
       </c>
       <c r="P35" t="n">
-        <v>3.21353933909168</v>
+        <v>3.232472214044309</v>
       </c>
       <c r="Q35" t="n">
-        <v>1198.01120699369</v>
+        <v>1198.646314119038</v>
       </c>
       <c r="R35" t="n">
-        <v>10116.01033592224</v>
+        <v>8100.919000387192</v>
       </c>
       <c r="S35" t="n">
-        <v>-8.234132000104431e-06</v>
+        <v>-1.213248280418264e-05</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SCT-36</t>
+          <t>SCT-21</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>720000</v>
+        <v>1300000</v>
       </c>
       <c r="E36" t="n">
         <v>0.0003</v>
@@ -2773,37 +2773,37 @@
         <v>0.95</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.08580132291894661</v>
+        <v>-0.07821390980803139</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.1000000014901161</v>
+        <v>-0.3636363744735718</v>
       </c>
       <c r="M36" t="n">
-        <v>864.1929321289062</v>
+        <v>883.3144681490385</v>
       </c>
       <c r="N36" t="n">
-        <v>0.0169030740747557</v>
+        <v>0.01725451249318818</v>
       </c>
       <c r="O36" t="n">
-        <v>0.002081888448789387</v>
+        <v>0.001746478429928781</v>
       </c>
       <c r="P36" t="n">
-        <v>3.227160728141053</v>
+        <v>3.202359318733215</v>
       </c>
       <c r="Q36" t="n">
-        <v>1198.747615559896</v>
+        <v>1189.500042854471</v>
       </c>
       <c r="R36" t="n">
-        <v>10101.70520925522</v>
+        <v>14756.54293203354</v>
       </c>
       <c r="S36" t="n">
-        <v>-8.493746465728888e-06</v>
+        <v>-5.300286806216953e-06</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SCT-37</t>
+          <t>SCT-22</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2817,7 +2817,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>730000</v>
+        <v>1290000</v>
       </c>
       <c r="E37" t="n">
         <v>0.0003</v>
@@ -2838,37 +2838,37 @@
         <v>0.95</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.05357907804156564</v>
+        <v>-0.04709835156307433</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.2000000029802322</v>
+        <v>-0.3333333432674408</v>
       </c>
       <c r="M37" t="n">
-        <v>850.0035308419841</v>
+        <v>927.1865910966267</v>
       </c>
       <c r="N37" t="n">
-        <v>0.01728696239126079</v>
+        <v>0.01703438789473247</v>
       </c>
       <c r="O37" t="n">
-        <v>0.002064280698558672</v>
+        <v>0.00102745947567843</v>
       </c>
       <c r="P37" t="n">
-        <v>3.218717761235694</v>
+        <v>3.203014880187752</v>
       </c>
       <c r="Q37" t="n">
-        <v>1205.293806966146</v>
+        <v>1202.510055763134</v>
       </c>
       <c r="R37" t="n">
-        <v>10072.44229340553</v>
+        <v>14736.30408143997</v>
       </c>
       <c r="S37" t="n">
-        <v>-5.319373045864366e-06</v>
+        <v>-3.196076255130592e-06</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SCT-38</t>
+          <t>SCT-23</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2882,7 +2882,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>410000</v>
+        <v>1290000</v>
       </c>
       <c r="E38" t="n">
         <v>0.0003</v>
@@ -2903,37 +2903,37 @@
         <v>0.95</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.08285833680115286</v>
+        <v>-0.06172820547227423</v>
       </c>
       <c r="L38" t="n">
-        <v>0.06693999469280243</v>
+        <v>-0.02329999580979347</v>
       </c>
       <c r="M38" t="n">
-        <v>849.8902951195126</v>
+        <v>872.4737350109011</v>
       </c>
       <c r="N38" t="n">
-        <v>0.0169603805989027</v>
+        <v>0.01681118815516432</v>
       </c>
       <c r="O38" t="n">
-        <v>0.002143289164738044</v>
+        <v>0.001759909112214094</v>
       </c>
       <c r="P38" t="n">
-        <v>3.245177745819092</v>
+        <v>3.188865291979886</v>
       </c>
       <c r="Q38" t="n">
-        <v>1200.29835679796</v>
+        <v>1197.716013382892</v>
       </c>
       <c r="R38" t="n">
-        <v>5452.257261514664</v>
+        <v>14722.9565551281</v>
       </c>
       <c r="S38" t="n">
-        <v>-1.519707028243462e-05</v>
+        <v>-4.192650113524509e-06</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SCT-39</t>
+          <t>SCT-24</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>380000</v>
+        <v>620000</v>
       </c>
       <c r="E39" t="n">
         <v>0.0003</v>
@@ -2968,37 +2968,37 @@
         <v>0.95</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.06918928221367844</v>
+        <v>-0.08076840271279516</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>0.1558909118175507</v>
       </c>
       <c r="M39" t="n">
-        <v>876.8114847322789</v>
+        <v>809.3843196745842</v>
       </c>
       <c r="N39" t="n">
-        <v>0.01675602203855912</v>
+        <v>0.01709947157008895</v>
       </c>
       <c r="O39" t="n">
-        <v>0.002021084550910423</v>
+        <v>0.002677177145258234</v>
       </c>
       <c r="P39" t="n">
-        <v>3.216466327992881</v>
+        <v>3.213665427700166</v>
       </c>
       <c r="Q39" t="n">
-        <v>1198.453630719866</v>
+        <v>1196.785132271903</v>
       </c>
       <c r="R39" t="n">
-        <v>5437.8234167099</v>
+        <v>9304.627391815186</v>
       </c>
       <c r="S39" t="n">
-        <v>-1.272370890181291e-05</v>
+        <v>-8.680455359646435e-06</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SCT-40</t>
+          <t>SCT-25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3012,7 +3012,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>400000</v>
+        <v>620000</v>
       </c>
       <c r="E40" t="n">
         <v>0.0003</v>
@@ -3033,37 +3033,37 @@
         <v>0.95</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.05729446642770909</v>
+        <v>-0.06089504700784962</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.1000000014901161</v>
+        <v>-0.1562909036874771</v>
       </c>
       <c r="M40" t="n">
-        <v>873.4272952196075</v>
+        <v>850.7828113186744</v>
       </c>
       <c r="N40" t="n">
-        <v>0.01716148578806927</v>
+        <v>0.0173359208515492</v>
       </c>
       <c r="O40" t="n">
-        <v>0.001847159338084518</v>
+        <v>0.00212054752820881</v>
       </c>
       <c r="P40" t="n">
-        <v>3.232732301805077</v>
+        <v>3.223078893076989</v>
       </c>
       <c r="Q40" t="n">
-        <v>1197.054809570312</v>
+        <v>1200.468372051532</v>
       </c>
       <c r="R40" t="n">
-        <v>5414.009315252304</v>
+        <v>9284.246625423431</v>
       </c>
       <c r="S40" t="n">
-        <v>-1.058263166749632e-05</v>
+        <v>-6.558964821237969e-06</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SCT-41</t>
+          <t>SCT-26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3077,7 +3077,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>410000</v>
+        <v>620000</v>
       </c>
       <c r="E41" t="n">
         <v>0.0003</v>
@@ -3098,37 +3098,37 @@
         <v>0.95</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.05091969369024765</v>
+        <v>-0.08695605206077979</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.09367619454860687</v>
+        <v>-0.4781684279441833</v>
       </c>
       <c r="M41" t="n">
-        <v>856.365341558689</v>
+        <v>778.2292283581149</v>
       </c>
       <c r="N41" t="n">
-        <v>0.01621380335602321</v>
+        <v>0.01692195176812155</v>
       </c>
       <c r="O41" t="n">
-        <v>0.002174257490447704</v>
+        <v>0.003309059979593648</v>
       </c>
       <c r="P41" t="n">
-        <v>3.210256012474618</v>
+        <v>3.207571560336698</v>
       </c>
       <c r="Q41" t="n">
-        <v>1201.771710564108</v>
+        <v>1197.860078456038</v>
       </c>
       <c r="R41" t="n">
-        <v>5398.00560760498</v>
+        <v>9270.770953893661</v>
       </c>
       <c r="S41" t="n">
-        <v>-9.433056834640824e-06</v>
+        <v>-9.379592322282413e-06</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SCT-42</t>
+          <t>SCT-27</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3142,7 +3142,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>3000000</v>
+        <v>1480000</v>
       </c>
       <c r="E42" t="n">
         <v>0.0003</v>
@@ -3163,37 +3163,37 @@
         <v>0.95</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.03691293662918421</v>
+        <v>-0.03887055685422761</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.1796254813671112</v>
+        <v>0.04770307615399361</v>
       </c>
       <c r="M42" t="n">
-        <v>707.6654290771485</v>
+        <v>466.1728206840721</v>
       </c>
       <c r="N42" t="n">
-        <v>0.01665242814591953</v>
+        <v>0.01646833285095467</v>
       </c>
       <c r="O42" t="n">
-        <v>0.01141412125783664</v>
+        <v>0.01808865653668139</v>
       </c>
       <c r="P42" t="n">
-        <v>3.116341458161672</v>
+        <v>3.096878704187032</v>
       </c>
       <c r="Q42" t="n">
-        <v>1218.383306329901</v>
+        <v>1241.916709586366</v>
       </c>
       <c r="R42" t="n">
-        <v>36672.48187422752</v>
+        <v>20326.9064142704</v>
       </c>
       <c r="S42" t="n">
-        <v>-1.006556817064669e-06</v>
+        <v>-1.912271157353228e-06</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SCT-43</t>
+          <t>SCT-28</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3207,7 +3207,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2980000</v>
+        <v>950000</v>
       </c>
       <c r="E43" t="n">
         <v>0.0003</v>
@@ -3228,37 +3228,37 @@
         <v>0.95</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.02299813292433269</v>
+        <v>-0.02410208596379165</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>941.8944393931038</v>
+        <v>952.9241615653838</v>
       </c>
       <c r="N43" t="n">
-        <v>0.01664669015076306</v>
+        <v>0.01708082157625433</v>
       </c>
       <c r="O43" t="n">
-        <v>0.0007859000304741369</v>
+        <v>0.000636368792025561</v>
       </c>
       <c r="P43" t="n">
-        <v>3.116607059275985</v>
+        <v>3.043231468072674</v>
       </c>
       <c r="Q43" t="n">
-        <v>1202.597068966843</v>
+        <v>1202.217054887251</v>
       </c>
       <c r="R43" t="n">
-        <v>36663.43608546257</v>
+        <v>20324.13341164589</v>
       </c>
       <c r="S43" t="n">
-        <v>-6.272770743779712e-07</v>
+        <v>-1.185885049838384e-06</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SCT-44</t>
+          <t>SCT-29</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3272,7 +3272,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2990000</v>
+        <v>1490000</v>
       </c>
       <c r="E44" t="n">
         <v>0.0003</v>
@@ -3293,37 +3293,37 @@
         <v>0.95</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.03965435168524541</v>
+        <v>-0.0625108793399753</v>
       </c>
       <c r="L44" t="n">
-        <v>0.1010571494698524</v>
+        <v>0.04741666465997696</v>
       </c>
       <c r="M44" t="n">
-        <v>897.0473032667485</v>
+        <v>800.0971218851589</v>
       </c>
       <c r="N44" t="n">
-        <v>0.01652318728993908</v>
+        <v>0.01720528434152188</v>
       </c>
       <c r="O44" t="n">
-        <v>0.001429477613824524</v>
+        <v>0.003114550544220644</v>
       </c>
       <c r="P44" t="n">
-        <v>3.160904287095851</v>
+        <v>3.174362001803097</v>
       </c>
       <c r="Q44" t="n">
-        <v>1206.064004010695</v>
+        <v>1209.78265953064</v>
       </c>
       <c r="R44" t="n">
-        <v>36655.16245150566</v>
+        <v>20324.03649783134</v>
       </c>
       <c r="S44" t="n">
-        <v>-1.081821741690755e-06</v>
+        <v>-3.075711822631565e-06</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SCT-45</t>
+          <t>SCT-30</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3337,7 +3337,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>3000000</v>
+        <v>770000</v>
       </c>
       <c r="E45" t="n">
         <v>0.0003</v>
@@ -3358,37 +3358,37 @@
         <v>0.95</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.05323140198694697</v>
+        <v>-0.05482129686868858</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.1666666716337204</v>
+        <v>0.1436000019311905</v>
       </c>
       <c r="M45" t="n">
-        <v>918.0664933268229</v>
+        <v>884.974719555347</v>
       </c>
       <c r="N45" t="n">
-        <v>0.01674220518698152</v>
+        <v>0.01615734424974237</v>
       </c>
       <c r="O45" t="n">
-        <v>0.001217376997552071</v>
+        <v>0.001539779463044916</v>
       </c>
       <c r="P45" t="n">
-        <v>3.168612830638886</v>
+        <v>3.204005222815972</v>
       </c>
       <c r="Q45" t="n">
-        <v>1205.241919381278</v>
+        <v>1193.449300797259</v>
       </c>
       <c r="R45" t="n">
-        <v>36608.00826907158</v>
+        <v>9646.979743719101</v>
       </c>
       <c r="S45" t="n">
-        <v>-1.454091727572072e-06</v>
+        <v>-5.682741990246358e-06</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SCT-46</t>
+          <t>SCT-31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3402,19 +3402,19 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1310000</v>
+        <v>760000</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0007683868659626061</v>
+        <v>0.0003</v>
       </c>
       <c r="F46" t="n">
         <v>3</v>
       </c>
       <c r="G46" t="n">
-        <v>8999</v>
+        <v>2048</v>
       </c>
       <c r="H46" t="n">
-        <v>68891</v>
+        <v>20480</v>
       </c>
       <c r="I46" t="n">
         <v>0.99</v>
@@ -3423,37 +3423,37 @@
         <v>0.95</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.0574820542912648</v>
+        <v>-0.03643133456353098</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>-0.04510000348091125</v>
       </c>
       <c r="M46" t="n">
-        <v>891.1868110425545</v>
+        <v>838.6874678762335</v>
       </c>
       <c r="N46" t="n">
-        <v>0.01386905341808285</v>
+        <v>0.01671373338571617</v>
       </c>
       <c r="O46" t="n">
-        <v>0.0016475375824874</v>
+        <v>0.002221554686314318</v>
       </c>
       <c r="P46" t="n">
-        <v>3.238080089742487</v>
+        <v>3.221089316041846</v>
       </c>
       <c r="Q46" t="n">
-        <v>1203.057855841819</v>
+        <v>1202.740619962178</v>
       </c>
       <c r="R46" t="n">
-        <v>16532.60478854179</v>
+        <v>9625.807464122772</v>
       </c>
       <c r="S46" t="n">
-        <v>-3.47689036461476e-06</v>
+        <v>-3.784756208693924e-06</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SCT-47</t>
+          <t>SCT-32</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3467,19 +3467,19 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1250000</v>
+        <v>770000</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0007683868659626061</v>
+        <v>0.0003</v>
       </c>
       <c r="F47" t="n">
         <v>3</v>
       </c>
       <c r="G47" t="n">
-        <v>8999</v>
+        <v>2048</v>
       </c>
       <c r="H47" t="n">
-        <v>68891</v>
+        <v>20480</v>
       </c>
       <c r="I47" t="n">
         <v>0.99</v>
@@ -3488,37 +3488,37 @@
         <v>0.95</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.05833676069229841</v>
+        <v>-0.06088397360418911</v>
       </c>
       <c r="L47" t="n">
-        <v>0.02182221412658691</v>
+        <v>0.03985454514622688</v>
       </c>
       <c r="M47" t="n">
-        <v>707.167419921875</v>
+        <v>853.4246199967025</v>
       </c>
       <c r="N47" t="n">
-        <v>0.008030062240055379</v>
+        <v>0.0168667607275503</v>
       </c>
       <c r="O47" t="n">
-        <v>0.006868942835888661</v>
+        <v>0.002109424436431644</v>
       </c>
       <c r="P47" t="n">
-        <v>3.213289976119995</v>
+        <v>3.21989875954467</v>
       </c>
       <c r="Q47" t="n">
-        <v>1209.14381475034</v>
+        <v>1199.984812266791</v>
       </c>
       <c r="R47" t="n">
-        <v>16501.31502985954</v>
+        <v>9614.763172388077</v>
       </c>
       <c r="S47" t="n">
-        <v>-3.535279496618093e-06</v>
+        <v>-6.332342514586034e-06</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SCT-48</t>
+          <t>SCT-33</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3532,19 +3532,19 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1870000</v>
+        <v>1590000</v>
       </c>
       <c r="E48" t="n">
-        <v>0.0007216260534285756</v>
+        <v>0.0003</v>
       </c>
       <c r="F48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G48" t="n">
-        <v>3523</v>
+        <v>2048</v>
       </c>
       <c r="H48" t="n">
-        <v>89004</v>
+        <v>20480</v>
       </c>
       <c r="I48" t="n">
         <v>0.99</v>
@@ -3553,37 +3553,37 @@
         <v>0.95</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.03591962989399777</v>
+        <v>-0.04188887321144202</v>
       </c>
       <c r="L48" t="n">
-        <v>0.04636363685131073</v>
+        <v>0.3271910548210144</v>
       </c>
       <c r="M48" t="n">
-        <v>942.6166476489389</v>
+        <v>726.0532055740837</v>
       </c>
       <c r="N48" t="n">
-        <v>0.0105044692976489</v>
+        <v>0.01691138584519157</v>
       </c>
       <c r="O48" t="n">
-        <v>0.0006557575244352098</v>
+        <v>0.006647793710059788</v>
       </c>
       <c r="P48" t="n">
-        <v>3.136978102240333</v>
+        <v>3.142067582352357</v>
       </c>
       <c r="Q48" t="n">
-        <v>1200.743687421426</v>
+        <v>1214.107131465789</v>
       </c>
       <c r="R48" t="n">
-        <v>16497.96086525917</v>
+        <v>15146.50751519203</v>
       </c>
       <c r="S48" t="n">
-        <v>-2.177216335240319e-06</v>
+        <v>-2.76557966709007e-06</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SCT-49</t>
+          <t>SCT-34</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3597,19 +3597,19 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2650000</v>
+        <v>730000</v>
       </c>
       <c r="E49" t="n">
-        <v>0.0007216260534285756</v>
+        <v>0.0003</v>
       </c>
       <c r="F49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G49" t="n">
-        <v>3523</v>
+        <v>2048</v>
       </c>
       <c r="H49" t="n">
-        <v>89004</v>
+        <v>20480</v>
       </c>
       <c r="I49" t="n">
         <v>0.99</v>
@@ -3618,37 +3618,37 @@
         <v>0.95</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.06752554793262257</v>
+        <v>-0.0632665089398546</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.1309521645307541</v>
+        <v>0.4811508655548096</v>
       </c>
       <c r="M49" t="n">
-        <v>679.2271453857422</v>
+        <v>583.2877704150056</v>
       </c>
       <c r="N49" t="n">
-        <v>0.0125180171353036</v>
+        <v>0.01691351620042149</v>
       </c>
       <c r="O49" t="n">
-        <v>0.1026605855862225</v>
+        <v>0.008947532817461145</v>
       </c>
       <c r="P49" t="n">
-        <v>3.206811978682032</v>
+        <v>3.175101247552323</v>
       </c>
       <c r="Q49" t="n">
-        <v>1215.782703145345</v>
+        <v>1210.351660834418</v>
       </c>
       <c r="R49" t="n">
-        <v>20327.0623216629</v>
+        <v>10138.08539009094</v>
       </c>
       <c r="S49" t="n">
-        <v>-3.321953111771563e-06</v>
+        <v>-6.240478996329214e-06</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SCT-50</t>
+          <t>SCT-35</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3662,19 +3662,19 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1480000</v>
+        <v>730000</v>
       </c>
       <c r="E50" t="n">
-        <v>0.0002591168778949834</v>
+        <v>0.0003</v>
       </c>
       <c r="F50" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G50" t="n">
-        <v>5559</v>
+        <v>2048</v>
       </c>
       <c r="H50" t="n">
-        <v>12971</v>
+        <v>20480</v>
       </c>
       <c r="I50" t="n">
         <v>0.99</v>
@@ -3683,37 +3683,37 @@
         <v>0.95</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.06037834857238968</v>
+        <v>-0.08329656442040451</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>0.005119999870657921</v>
       </c>
       <c r="M50" t="n">
-        <v>874.421417834712</v>
+        <v>908.7330548012093</v>
       </c>
       <c r="N50" t="n">
-        <v>0.01145707618664293</v>
+        <v>0.01671572432250661</v>
       </c>
       <c r="O50" t="n">
-        <v>0.00290804953478715</v>
+        <v>0.001475003170686678</v>
       </c>
       <c r="P50" t="n">
-        <v>3.176239086911569</v>
+        <v>3.21353933909168</v>
       </c>
       <c r="Q50" t="n">
-        <v>1214.048692830404</v>
+        <v>1198.01120699369</v>
       </c>
       <c r="R50" t="n">
-        <v>19083.27363753319</v>
+        <v>10116.01033592224</v>
       </c>
       <c r="S50" t="n">
-        <v>-3.163940826883963e-06</v>
+        <v>-8.234132000104431e-06</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SCT-51</t>
+          <t>SCT-36</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3727,19 +3727,19 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1960000</v>
+        <v>720000</v>
       </c>
       <c r="E51" t="n">
-        <v>0.0007197620880058231</v>
+        <v>0.0003</v>
       </c>
       <c r="F51" t="n">
         <v>3</v>
       </c>
       <c r="G51" t="n">
-        <v>1706</v>
+        <v>2048</v>
       </c>
       <c r="H51" t="n">
-        <v>79501</v>
+        <v>20480</v>
       </c>
       <c r="I51" t="n">
         <v>0.99</v>
@@ -3748,37 +3748,37 @@
         <v>0.95</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.04389371709676568</v>
+        <v>-0.08580132291894661</v>
       </c>
       <c r="L51" t="n">
-        <v>0.123871847987175</v>
+        <v>-0.1000000014901161</v>
       </c>
       <c r="M51" t="n">
-        <v>567.0420322807468</v>
+        <v>864.1929321289062</v>
       </c>
       <c r="N51" t="n">
-        <v>0.008433592948619719</v>
+        <v>0.0169030740747557</v>
       </c>
       <c r="O51" t="n">
-        <v>0.01632468533075251</v>
+        <v>0.002081888448789387</v>
       </c>
       <c r="P51" t="n">
-        <v>3.025004586394952</v>
+        <v>3.227160728141053</v>
       </c>
       <c r="Q51" t="n">
-        <v>1216.654144965278</v>
+        <v>1198.747615559896</v>
       </c>
       <c r="R51" t="n">
-        <v>23761.25207018852</v>
+        <v>10101.70520925522</v>
       </c>
       <c r="S51" t="n">
-        <v>-1.847281320323851e-06</v>
+        <v>-8.493746465728888e-06</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SCT-52</t>
+          <t>SCT-37</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3792,19 +3792,19 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1690000</v>
+        <v>730000</v>
       </c>
       <c r="E52" t="n">
-        <v>0.0007551567208135385</v>
+        <v>0.0003</v>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G52" t="n">
-        <v>1787</v>
+        <v>2048</v>
       </c>
       <c r="H52" t="n">
-        <v>13451</v>
+        <v>20480</v>
       </c>
       <c r="I52" t="n">
         <v>0.99</v>
@@ -3813,37 +3813,37 @@
         <v>0.95</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.04540139970992356</v>
+        <v>-0.05357907804156564</v>
       </c>
       <c r="L52" t="n">
-        <v>-0.07420951873064041</v>
+        <v>-0.2000000029802322</v>
       </c>
       <c r="M52" t="n">
-        <v>786.2223196537537</v>
+        <v>850.0035308419841</v>
       </c>
       <c r="N52" t="n">
-        <v>0.01498682993023019</v>
+        <v>0.01728696239126079</v>
       </c>
       <c r="O52" t="n">
-        <v>0.002061714882361948</v>
+        <v>0.002064280698558672</v>
       </c>
       <c r="P52" t="n">
-        <v>3.126439815442238</v>
+        <v>3.218717761235694</v>
       </c>
       <c r="Q52" t="n">
-        <v>1198.956001177226</v>
+        <v>1205.293806966146</v>
       </c>
       <c r="R52" t="n">
-        <v>17330.89785933495</v>
+        <v>10072.44229340553</v>
       </c>
       <c r="S52" t="n">
-        <v>-2.619679607970743e-06</v>
+        <v>-5.319373045864366e-06</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SCT-54</t>
+          <t>SCT-38</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3857,19 +3857,19 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>960000</v>
+        <v>410000</v>
       </c>
       <c r="E53" t="n">
-        <v>0.0007551567208135385</v>
+        <v>0.0003</v>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G53" t="n">
-        <v>1787</v>
+        <v>2048</v>
       </c>
       <c r="H53" t="n">
-        <v>13451</v>
+        <v>20480</v>
       </c>
       <c r="I53" t="n">
         <v>0.99</v>
@@ -3878,96 +3878,5399 @@
         <v>0.95</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.03446620497622158</v>
+        <v>-0.08285833680115286</v>
       </c>
       <c r="L53" t="n">
-        <v>-0.1818181872367859</v>
+        <v>0.06693999469280243</v>
       </c>
       <c r="M53" t="n">
-        <v>901.5920035044352</v>
+        <v>849.8902951195126</v>
       </c>
       <c r="N53" t="n">
-        <v>0.01754029887502618</v>
+        <v>0.0169603805989027</v>
       </c>
       <c r="O53" t="n">
-        <v>0.002309903035834516</v>
+        <v>0.002143289164738044</v>
       </c>
       <c r="P53" t="n">
-        <v>3.215656240781148</v>
+        <v>3.245177745819092</v>
       </c>
       <c r="Q53" t="n">
-        <v>1206.890709661668</v>
+        <v>1200.29835679796</v>
       </c>
       <c r="R53" t="n">
-        <v>10222.97701406479</v>
+        <v>5452.257261514664</v>
       </c>
       <c r="S53" t="n">
-        <v>-3.37144502318678e-06</v>
+        <v>-1.519707028243462e-05</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>SCT-39</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>380000</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F54" t="n">
+        <v>3</v>
+      </c>
+      <c r="G54" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H54" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K54" t="n">
+        <v>-0.06918928221367844</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>876.8114847322789</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0.01675602203855912</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0.002021084550910423</v>
+      </c>
+      <c r="P54" t="n">
+        <v>3.216466327992881</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>1198.453630719866</v>
+      </c>
+      <c r="R54" t="n">
+        <v>5437.8234167099</v>
+      </c>
+      <c r="S54" t="n">
+        <v>-1.272370890181291e-05</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>SCT-40</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>400000</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F55" t="n">
+        <v>3</v>
+      </c>
+      <c r="G55" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H55" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K55" t="n">
+        <v>-0.05729446642770909</v>
+      </c>
+      <c r="L55" t="n">
+        <v>-0.1000000014901161</v>
+      </c>
+      <c r="M55" t="n">
+        <v>873.4272952196075</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0.01716148578806927</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0.001847159338084518</v>
+      </c>
+      <c r="P55" t="n">
+        <v>3.232732301805077</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>1197.054809570312</v>
+      </c>
+      <c r="R55" t="n">
+        <v>5414.009315252304</v>
+      </c>
+      <c r="S55" t="n">
+        <v>-1.058263166749632e-05</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SCT-41</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>410000</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F56" t="n">
+        <v>3</v>
+      </c>
+      <c r="G56" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H56" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K56" t="n">
+        <v>-0.05091969369024765</v>
+      </c>
+      <c r="L56" t="n">
+        <v>-0.09367619454860687</v>
+      </c>
+      <c r="M56" t="n">
+        <v>856.365341558689</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0.01621380335602321</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0.002174257490447704</v>
+      </c>
+      <c r="P56" t="n">
+        <v>3.210256012474618</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>1201.771710564108</v>
+      </c>
+      <c r="R56" t="n">
+        <v>5398.00560760498</v>
+      </c>
+      <c r="S56" t="n">
+        <v>-9.433056834640824e-06</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>SCT-42</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F57" t="n">
+        <v>3</v>
+      </c>
+      <c r="G57" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H57" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K57" t="n">
+        <v>-0.03691293662918421</v>
+      </c>
+      <c r="L57" t="n">
+        <v>-0.1796254813671112</v>
+      </c>
+      <c r="M57" t="n">
+        <v>707.6654290771485</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0.01665242814591953</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0.01141412125783664</v>
+      </c>
+      <c r="P57" t="n">
+        <v>3.116341458161672</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>1218.383306329901</v>
+      </c>
+      <c r="R57" t="n">
+        <v>36672.48187422752</v>
+      </c>
+      <c r="S57" t="n">
+        <v>-1.006556817064669e-06</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>SCT-43</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>2980000</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F58" t="n">
+        <v>3</v>
+      </c>
+      <c r="G58" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H58" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K58" t="n">
+        <v>-0.02299813292433269</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>941.8944393931038</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0.01664669015076306</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0.0007859000304741369</v>
+      </c>
+      <c r="P58" t="n">
+        <v>3.116607059275985</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>1202.597068966843</v>
+      </c>
+      <c r="R58" t="n">
+        <v>36663.43608546257</v>
+      </c>
+      <c r="S58" t="n">
+        <v>-6.272770743779712e-07</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>SCT-44</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>2990000</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F59" t="n">
+        <v>3</v>
+      </c>
+      <c r="G59" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H59" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K59" t="n">
+        <v>-0.03965435168524541</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.1010571494698524</v>
+      </c>
+      <c r="M59" t="n">
+        <v>897.0473032667485</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0.01652318728993908</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0.001429477613824524</v>
+      </c>
+      <c r="P59" t="n">
+        <v>3.160904287095851</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>1206.064004010695</v>
+      </c>
+      <c r="R59" t="n">
+        <v>36655.16245150566</v>
+      </c>
+      <c r="S59" t="n">
+        <v>-1.081821741690755e-06</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>SCT-45</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F60" t="n">
+        <v>3</v>
+      </c>
+      <c r="G60" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H60" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K60" t="n">
+        <v>-0.05323140198694697</v>
+      </c>
+      <c r="L60" t="n">
+        <v>-0.1666666716337204</v>
+      </c>
+      <c r="M60" t="n">
+        <v>918.0664933268229</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0.01674220518698152</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.001217376997552071</v>
+      </c>
+      <c r="P60" t="n">
+        <v>3.168612830638886</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>1205.241919381278</v>
+      </c>
+      <c r="R60" t="n">
+        <v>36608.00826907158</v>
+      </c>
+      <c r="S60" t="n">
+        <v>-1.454091727572072e-06</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>SCT-46</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>1310000</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.0007683868659626061</v>
+      </c>
+      <c r="F61" t="n">
+        <v>3</v>
+      </c>
+      <c r="G61" t="n">
+        <v>8999</v>
+      </c>
+      <c r="H61" t="n">
+        <v>68891</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K61" t="n">
+        <v>-0.0574820542912648</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>891.1868110425545</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0.01386905341808285</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0.0016475375824874</v>
+      </c>
+      <c r="P61" t="n">
+        <v>3.238080089742487</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>1203.057855841819</v>
+      </c>
+      <c r="R61" t="n">
+        <v>16532.60478854179</v>
+      </c>
+      <c r="S61" t="n">
+        <v>-3.47689036461476e-06</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>SCT-47</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>1250000</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.0007683868659626061</v>
+      </c>
+      <c r="F62" t="n">
+        <v>3</v>
+      </c>
+      <c r="G62" t="n">
+        <v>8999</v>
+      </c>
+      <c r="H62" t="n">
+        <v>68891</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K62" t="n">
+        <v>-0.05833676069229841</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.02182221412658691</v>
+      </c>
+      <c r="M62" t="n">
+        <v>707.167419921875</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0.008030062240055379</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0.006868942835888661</v>
+      </c>
+      <c r="P62" t="n">
+        <v>3.213289976119995</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>1209.14381475034</v>
+      </c>
+      <c r="R62" t="n">
+        <v>16501.31502985954</v>
+      </c>
+      <c r="S62" t="n">
+        <v>-3.535279496618093e-06</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>SCT-48</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>1870000</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.0007216260534285756</v>
+      </c>
+      <c r="F63" t="n">
+        <v>2</v>
+      </c>
+      <c r="G63" t="n">
+        <v>3523</v>
+      </c>
+      <c r="H63" t="n">
+        <v>89004</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K63" t="n">
+        <v>-0.03591962989399777</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0.04636363685131073</v>
+      </c>
+      <c r="M63" t="n">
+        <v>942.6166476489389</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0.0105044692976489</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0.0006557575244352098</v>
+      </c>
+      <c r="P63" t="n">
+        <v>3.136978102240333</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>1200.743687421426</v>
+      </c>
+      <c r="R63" t="n">
+        <v>16497.96086525917</v>
+      </c>
+      <c r="S63" t="n">
+        <v>-2.177216335240319e-06</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>SCT-49</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>2650000</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.0007216260534285756</v>
+      </c>
+      <c r="F64" t="n">
+        <v>2</v>
+      </c>
+      <c r="G64" t="n">
+        <v>3523</v>
+      </c>
+      <c r="H64" t="n">
+        <v>89004</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K64" t="n">
+        <v>-0.06752554793262257</v>
+      </c>
+      <c r="L64" t="n">
+        <v>-0.1309521645307541</v>
+      </c>
+      <c r="M64" t="n">
+        <v>679.2271453857422</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0.0125180171353036</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0.1026605855862225</v>
+      </c>
+      <c r="P64" t="n">
+        <v>3.206811978682032</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>1215.782703145345</v>
+      </c>
+      <c r="R64" t="n">
+        <v>20327.0623216629</v>
+      </c>
+      <c r="S64" t="n">
+        <v>-3.321953111771563e-06</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>SCT-50</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>1480000</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.0002591168778949834</v>
+      </c>
+      <c r="F65" t="n">
+        <v>8</v>
+      </c>
+      <c r="G65" t="n">
+        <v>5559</v>
+      </c>
+      <c r="H65" t="n">
+        <v>12971</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K65" t="n">
+        <v>-0.06037834857238968</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>874.421417834712</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0.01145707618664293</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0.00290804953478715</v>
+      </c>
+      <c r="P65" t="n">
+        <v>3.176239086911569</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>1214.048692830404</v>
+      </c>
+      <c r="R65" t="n">
+        <v>19083.27363753319</v>
+      </c>
+      <c r="S65" t="n">
+        <v>-3.163940826883963e-06</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>SCT-51</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>1960000</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.0007197620880058231</v>
+      </c>
+      <c r="F66" t="n">
+        <v>3</v>
+      </c>
+      <c r="G66" t="n">
+        <v>1706</v>
+      </c>
+      <c r="H66" t="n">
+        <v>79501</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K66" t="n">
+        <v>-0.04389371709676568</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0.123871847987175</v>
+      </c>
+      <c r="M66" t="n">
+        <v>567.0420322807468</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0.008433592948619719</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0.01632468533075251</v>
+      </c>
+      <c r="P66" t="n">
+        <v>3.025004586394952</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>1216.654144965278</v>
+      </c>
+      <c r="R66" t="n">
+        <v>23761.25207018852</v>
+      </c>
+      <c r="S66" t="n">
+        <v>-1.847281320323851e-06</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>SCT-52</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>1690000</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.0007551567208135385</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" t="n">
+        <v>1787</v>
+      </c>
+      <c r="H67" t="n">
+        <v>13451</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K67" t="n">
+        <v>-0.04540139970992356</v>
+      </c>
+      <c r="L67" t="n">
+        <v>-0.07420951873064041</v>
+      </c>
+      <c r="M67" t="n">
+        <v>786.2223196537537</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0.01498682993023019</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0.002061714882361948</v>
+      </c>
+      <c r="P67" t="n">
+        <v>3.126439815442238</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>1198.956001177226</v>
+      </c>
+      <c r="R67" t="n">
+        <v>17330.89785933495</v>
+      </c>
+      <c r="S67" t="n">
+        <v>-2.619679607970743e-06</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>SCT-54</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>960000</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.0007551567208135385</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" t="n">
+        <v>1787</v>
+      </c>
+      <c r="H68" t="n">
+        <v>13451</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K68" t="n">
+        <v>-0.03446620497622158</v>
+      </c>
+      <c r="L68" t="n">
+        <v>-0.1818181872367859</v>
+      </c>
+      <c r="M68" t="n">
+        <v>901.5920035044352</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0.01754029887502618</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0.002309903035834516</v>
+      </c>
+      <c r="P68" t="n">
+        <v>3.215656240781148</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>1206.890709661668</v>
+      </c>
+      <c r="R68" t="n">
+        <v>10222.97701406479</v>
+      </c>
+      <c r="S68" t="n">
+        <v>-3.37144502318678e-06</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
           <t>SCT-9</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>SoccerTwos</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>poca</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
         <v>1600000</v>
       </c>
-      <c r="E54" t="n">
-        <v>0.0003</v>
-      </c>
-      <c r="F54" t="n">
-        <v>3</v>
-      </c>
-      <c r="G54" t="n">
-        <v>2048</v>
-      </c>
-      <c r="H54" t="n">
-        <v>20480</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="K54" t="n">
+      <c r="E69" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F69" t="n">
+        <v>3</v>
+      </c>
+      <c r="G69" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H69" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K69" t="n">
         <v>-0.04606686621409608</v>
       </c>
-      <c r="L54" t="n">
+      <c r="L69" t="n">
         <v>0.1815885752439499</v>
       </c>
-      <c r="M54" t="n">
+      <c r="M69" t="n">
         <v>563.7095175266265</v>
       </c>
-      <c r="N54" t="n">
+      <c r="N69" t="n">
         <v>0.0170133884002765</v>
       </c>
-      <c r="O54" t="n">
+      <c r="O69" t="n">
         <v>0.01267358388243792</v>
       </c>
-      <c r="P54" t="n">
+      <c r="P69" t="n">
         <v>3.122101083397865</v>
       </c>
-      <c r="Q54" t="n">
+      <c r="Q69" t="n">
         <v>1217.501893696032</v>
       </c>
-      <c r="R54" t="n">
+      <c r="R69" t="n">
         <v>17740.51610898972</v>
       </c>
-      <c r="S54" t="n">
+      <c r="S69" t="n">
         <v>-2.596703834943813e-06</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>1370000</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F70" t="n">
+        <v>3</v>
+      </c>
+      <c r="G70" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H70" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K70" t="n">
+        <v>-0.06449501164577032</v>
+      </c>
+      <c r="L70" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="M70" t="n">
+        <v>842.5506155195027</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0.01677780243612471</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0.002244662638206916</v>
+      </c>
+      <c r="P70" t="n">
+        <v>3.181490304696299</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>1201.726677008435</v>
+      </c>
+      <c r="R70" t="n">
+        <v>3.314389228820801</v>
+      </c>
+      <c r="S70" t="n">
+        <v>-0.01945909402702122</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>1410000</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F71" t="n">
+        <v>3</v>
+      </c>
+      <c r="G71" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H71" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K71" t="n">
+        <v>-0.02813724562664457</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0.03675918281078339</v>
+      </c>
+      <c r="M71" t="n">
+        <v>565.9702087294125</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0.01715694304386323</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0.01255561838016464</v>
+      </c>
+      <c r="P71" t="n">
+        <v>3.119588150200269</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>1221.224371563947</v>
+      </c>
+      <c r="R71" t="n">
+        <v>17995.36075329781</v>
+      </c>
+      <c r="S71" t="n">
+        <v>-1.563583304185118e-06</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F72" t="n">
+        <v>3</v>
+      </c>
+      <c r="G72" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H72" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K72" t="n">
+        <v>-0.2728000059723854</v>
+      </c>
+      <c r="L72" t="n">
+        <v>-0.1456000059843063</v>
+      </c>
+      <c r="M72" t="n">
+        <v>975.8333129882812</v>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>3.295733213424683</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>1199.126098632812</v>
+      </c>
+      <c r="R72" t="n">
+        <v>231.1879358291626</v>
+      </c>
+      <c r="S72" t="n">
+        <v>-0.001179992394473266</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>1530000</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F73" t="n">
+        <v>3</v>
+      </c>
+      <c r="G73" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H73" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K73" t="n">
+        <v>-0.06845330962533849</v>
+      </c>
+      <c r="L73" t="n">
+        <v>-0.1666666716337204</v>
+      </c>
+      <c r="M73" t="n">
+        <v>864.7286899541717</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0.01653499775369402</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0.001996715619869474</v>
+      </c>
+      <c r="P73" t="n">
+        <v>3.185842038759219</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>1196.510785381611</v>
+      </c>
+      <c r="R73" t="n">
+        <v>17995.40660214424</v>
+      </c>
+      <c r="S73" t="n">
+        <v>-3.803932366673057e-06</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F74" t="n">
+        <v>3</v>
+      </c>
+      <c r="G74" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H74" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K74" t="n">
+        <v>-0.028769226744771</v>
+      </c>
+      <c r="L74" t="n">
+        <v>-0.028769226744771</v>
+      </c>
+      <c r="M74" t="n">
+        <v>761.7142944335938</v>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>3.29572057723999</v>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R74" t="n">
+        <v>122.5535886287689</v>
+      </c>
+      <c r="S74" t="n">
+        <v>-0.0002347481380730254</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F75" t="n">
+        <v>3</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H75" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-0.0833333358168602</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.1666666716337204</v>
+      </c>
+      <c r="M75" t="n">
+        <v>999</v>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>3.295716047286987</v>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R75" t="n">
+        <v>222.6824479103088</v>
+      </c>
+      <c r="S75" t="n">
+        <v>-0.00037422498539456</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>1530000</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G76" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H76" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K76" t="n">
+        <v>-0.1056720826689617</v>
+      </c>
+      <c r="L76" t="n">
+        <v>-0.3168941140174866</v>
+      </c>
+      <c r="M76" t="n">
+        <v>782.8805366466248</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0.01738629845613745</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0.003405708882395706</v>
+      </c>
+      <c r="P76" t="n">
+        <v>3.17440099809684</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>1195.389624554178</v>
+      </c>
+      <c r="R76" t="n">
+        <v>17995.47889375687</v>
+      </c>
+      <c r="S76" t="n">
+        <v>-5.872146181429061e-06</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F77" t="n">
+        <v>3</v>
+      </c>
+      <c r="G77" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H77" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K77" t="n">
+        <v>-0.1117846146225929</v>
+      </c>
+      <c r="L77" t="n">
+        <v>-0.2235692292451859</v>
+      </c>
+      <c r="M77" t="n">
+        <v>999</v>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>3.295713186264038</v>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R77" t="n">
+        <v>225.3836541175842</v>
+      </c>
+      <c r="S77" t="n">
+        <v>-0.0004959748082009271</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F78" t="n">
+        <v>3</v>
+      </c>
+      <c r="G78" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H78" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K78" t="n">
+        <v>-0.0126383109697296</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0.3443664014339447</v>
+      </c>
+      <c r="M78" t="n">
+        <v>467.7886907450358</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0.01631009223471795</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0.02216387585254519</v>
+      </c>
+      <c r="P78" t="n">
+        <v>3.046110603014628</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>1253.373364592252</v>
+      </c>
+      <c r="R78" t="n">
+        <v>17995.3097422123</v>
+      </c>
+      <c r="S78" t="n">
+        <v>-7.023113883993572e-07</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>1510000</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F79" t="n">
+        <v>3</v>
+      </c>
+      <c r="G79" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H79" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K79" t="n">
+        <v>-0.07163368116476033</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>839.77405507941</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0.01651434392801353</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0.002660633123222007</v>
+      </c>
+      <c r="P79" t="n">
+        <v>3.195006257609317</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>1202.670620230741</v>
+      </c>
+      <c r="R79" t="n">
+        <v>17995.27819418907</v>
+      </c>
+      <c r="S79" t="n">
+        <v>-3.980693179163624e-06</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F80" t="n">
+        <v>3</v>
+      </c>
+      <c r="G80" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H80" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K80" t="n">
+        <v>-0.4000000059604645</v>
+      </c>
+      <c r="L80" t="n">
+        <v>-0.4000000059604645</v>
+      </c>
+      <c r="M80" t="n">
+        <v>676.25</v>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>3.295718193054199</v>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R80" t="n">
+        <v>124.5195536613464</v>
+      </c>
+      <c r="S80" t="n">
+        <v>-0.003212346930252715</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>1540000</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F81" t="n">
+        <v>3</v>
+      </c>
+      <c r="G81" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H81" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K81" t="n">
+        <v>-0.06445192188771393</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0.1344666630029678</v>
+      </c>
+      <c r="M81" t="n">
+        <v>904.1678835385806</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0.01636311886700946</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0.001482502024154822</v>
+      </c>
+      <c r="P81" t="n">
+        <v>3.179122814884434</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>1193.479008740718</v>
+      </c>
+      <c r="R81" t="n">
+        <v>17995.32134366035</v>
+      </c>
+      <c r="S81" t="n">
+        <v>-3.581593273988405e-06</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>1320000</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F82" t="n">
+        <v>3</v>
+      </c>
+      <c r="G82" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H82" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K82" t="n">
+        <v>-0.06664539988273507</v>
+      </c>
+      <c r="L82" t="n">
+        <v>-0.2310925424098969</v>
+      </c>
+      <c r="M82" t="n">
+        <v>687.3985456408876</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0.01708874385803938</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0.008011376763117842</v>
+      </c>
+      <c r="P82" t="n">
+        <v>3.15069091500658</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>1208.608882112323</v>
+      </c>
+      <c r="R82" t="n">
+        <v>17995.37686562538</v>
+      </c>
+      <c r="S82" t="n">
+        <v>-3.70347341877794e-06</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>1540000</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F83" t="n">
+        <v>3</v>
+      </c>
+      <c r="G83" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H83" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K83" t="n">
+        <v>-0.07360486720398358</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0.1564333289861679</v>
+      </c>
+      <c r="M83" t="n">
+        <v>830.1912564364346</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0.01694514940846974</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0.002487589927754221</v>
+      </c>
+      <c r="P83" t="n">
+        <v>3.181821561478949</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>1202.656204333408</v>
+      </c>
+      <c r="R83" t="n">
+        <v>17995.38477325439</v>
+      </c>
+      <c r="S83" t="n">
+        <v>-4.090208024525192e-06</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>1470000</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F84" t="n">
+        <v>3</v>
+      </c>
+      <c r="G84" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H84" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K84" t="n">
+        <v>-0.06332442711454303</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0.1802333295345306</v>
+      </c>
+      <c r="M84" t="n">
+        <v>730.2918465542956</v>
+      </c>
+      <c r="N84" t="n">
+        <v>0.01708946985137813</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0.006411157496712609</v>
+      </c>
+      <c r="P84" t="n">
+        <v>3.135813155141817</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>1204.924033929494</v>
+      </c>
+      <c r="R84" t="n">
+        <v>17995.27150392532</v>
+      </c>
+      <c r="S84" t="n">
+        <v>-3.518948135943935e-06</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>1570000</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F85" t="n">
+        <v>3</v>
+      </c>
+      <c r="G85" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H85" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K85" t="n">
+        <v>-0.03363346327155544</v>
+      </c>
+      <c r="L85" t="n">
+        <v>-0.07033684104681015</v>
+      </c>
+      <c r="M85" t="n">
+        <v>861.5773676975517</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0.01646376987143109</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0.001796836847432814</v>
+      </c>
+      <c r="P85" t="n">
+        <v>3.166345412564126</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>1215.392179631005</v>
+      </c>
+      <c r="R85" t="n">
+        <v>17995.39891505241</v>
+      </c>
+      <c r="S85" t="n">
+        <v>-1.869003484186306e-06</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>1660000</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F86" t="n">
+        <v>3</v>
+      </c>
+      <c r="G86" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H86" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K86" t="n">
+        <v>-0.06369531308356897</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0.3481379449367523</v>
+      </c>
+      <c r="M86" t="n">
+        <v>751.0875334222633</v>
+      </c>
+      <c r="N86" t="n">
+        <v>0.01645882996162037</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0.003862392731738887</v>
+      </c>
+      <c r="P86" t="n">
+        <v>3.175137179443635</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>1206.042582062752</v>
+      </c>
+      <c r="R86" t="n">
+        <v>19845.67032814026</v>
+      </c>
+      <c r="S86" t="n">
+        <v>-3.20953195484921e-06</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>1310000</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F87" t="n">
+        <v>3</v>
+      </c>
+      <c r="G87" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H87" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K87" t="n">
+        <v>-0.04088477553372645</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="n">
+        <v>928.0308892316879</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0.01652757000798981</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0.001104789863318584</v>
+      </c>
+      <c r="P87" t="n">
+        <v>3.151110061414682</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>1195.921754557292</v>
+      </c>
+      <c r="R87" t="n">
+        <v>17995.40541243553</v>
+      </c>
+      <c r="S87" t="n">
+        <v>-2.271956346450159e-06</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>1510000</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F88" t="n">
+        <v>3</v>
+      </c>
+      <c r="G88" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H88" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K88" t="n">
+        <v>-0.03980203662129329</v>
+      </c>
+      <c r="L88" t="n">
+        <v>-0.3361333310604095</v>
+      </c>
+      <c r="M88" t="n">
+        <v>801.8738742853632</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0.01624878589063883</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0.002943580341629318</v>
+      </c>
+      <c r="P88" t="n">
+        <v>3.178410193778032</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>1212.313703670058</v>
+      </c>
+      <c r="R88" t="n">
+        <v>17995.38080620766</v>
+      </c>
+      <c r="S88" t="n">
+        <v>-2.21179185091561e-06</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>1460000</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F89" t="n">
+        <v>3</v>
+      </c>
+      <c r="G89" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H89" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K89" t="n">
+        <v>-0.02161415235286145</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0.06669516116380692</v>
+      </c>
+      <c r="M89" t="n">
+        <v>575.3704257076733</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0.01681189608814962</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0.01445821519540486</v>
+      </c>
+      <c r="P89" t="n">
+        <v>3.126983565826939</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>1235.671848653889</v>
+      </c>
+      <c r="R89" t="n">
+        <v>17995.2579574585</v>
+      </c>
+      <c r="S89" t="n">
+        <v>-1.201102668489563e-06</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>1470000</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F90" t="n">
+        <v>3</v>
+      </c>
+      <c r="G90" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H90" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K90" t="n">
+        <v>-0.02799931811108314</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" t="n">
+        <v>970.6991652451552</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0.01681767647553768</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0.0009808229476512434</v>
+      </c>
+      <c r="P90" t="n">
+        <v>3.052977441193221</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>1192.919070773655</v>
+      </c>
+      <c r="R90" t="n">
+        <v>17995.34271717072</v>
+      </c>
+      <c r="S90" t="n">
+        <v>-1.555920248429994e-06</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>1430000</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F91" t="n">
+        <v>3</v>
+      </c>
+      <c r="G91" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H91" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K91" t="n">
+        <v>-0.05654290635334133</v>
+      </c>
+      <c r="L91" t="n">
+        <v>-0.2000000029802322</v>
+      </c>
+      <c r="M91" t="n">
+        <v>893.8520998654666</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0.01685132450339469</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0.001480786157119908</v>
+      </c>
+      <c r="P91" t="n">
+        <v>3.163388979184877</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>1193.870452231549</v>
+      </c>
+      <c r="R91" t="n">
+        <v>17995.38954687119</v>
+      </c>
+      <c r="S91" t="n">
+        <v>-3.142077375211492e-06</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>570000</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F92" t="n">
+        <v>3</v>
+      </c>
+      <c r="G92" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H92" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K92" t="n">
+        <v>-0.04783913694126041</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0.1037090942263603</v>
+      </c>
+      <c r="M92" t="n">
+        <v>871.1559426826343</v>
+      </c>
+      <c r="N92" t="n">
+        <v>0.01636776052272091</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0.00177967599386018</v>
+      </c>
+      <c r="P92" t="n">
+        <v>3.230961523557964</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>1196.959497625178</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6776.112241506577</v>
+      </c>
+      <c r="S92" t="n">
+        <v>-7.059968199497244e-06</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>1480000</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F93" t="n">
+        <v>3</v>
+      </c>
+      <c r="G93" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H93" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K93" t="n">
+        <v>-0.06202322707647302</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" t="n">
+        <v>874.6661499023437</v>
+      </c>
+      <c r="N93" t="n">
+        <v>0.01665779245018527</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0.00179455166468962</v>
+      </c>
+      <c r="P93" t="n">
+        <v>3.192651141484578</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>1207.600314558045</v>
+      </c>
+      <c r="R93" t="n">
+        <v>17995.39518928528</v>
+      </c>
+      <c r="S93" t="n">
+        <v>-3.446616560741192e-06</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>1460000</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F94" t="n">
+        <v>3</v>
+      </c>
+      <c r="G94" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H94" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K94" t="n">
+        <v>-0.08829976006870298</v>
+      </c>
+      <c r="L94" t="n">
+        <v>-0.3333333432674408</v>
+      </c>
+      <c r="M94" t="n">
+        <v>835.3426404979131</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0.01643654806956426</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0.002490366790140404</v>
+      </c>
+      <c r="P94" t="n">
+        <v>3.189848537314428</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>1199.59804608745</v>
+      </c>
+      <c r="R94" t="n">
+        <v>17995.3785841465</v>
+      </c>
+      <c r="S94" t="n">
+        <v>-4.906802024520505e-06</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>1370000</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F95" t="n">
+        <v>3</v>
+      </c>
+      <c r="G95" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H95" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0.01767039963173388</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0.03920650482177734</v>
+      </c>
+      <c r="M95" t="n">
+        <v>495.9913088387817</v>
+      </c>
+      <c r="N95" t="n">
+        <v>0.01710618726792745</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0.02207123090556706</v>
+      </c>
+      <c r="P95" t="n">
+        <v>3.100599236731982</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>1263.222676595052</v>
+      </c>
+      <c r="R95" t="n">
+        <v>17995.22323393822</v>
+      </c>
+      <c r="S95" t="n">
+        <v>9.819494541422671e-07</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>1440000</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F96" t="n">
+        <v>3</v>
+      </c>
+      <c r="G96" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H96" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K96" t="n">
+        <v>-0.02455217289550799</v>
+      </c>
+      <c r="L96" t="n">
+        <v>-0.3083965480327606</v>
+      </c>
+      <c r="M96" t="n">
+        <v>510.8669792281257</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0.0168292872772059</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0.01773892025470131</v>
+      </c>
+      <c r="P96" t="n">
+        <v>3.074720220433341</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>1242.419404820033</v>
+      </c>
+      <c r="R96" t="n">
+        <v>17995.25138044357</v>
+      </c>
+      <c r="S96" t="n">
+        <v>-1.364369542633352e-06</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>1480000</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F97" t="n">
+        <v>3</v>
+      </c>
+      <c r="G97" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H97" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K97" t="n">
+        <v>-0.02570734429723785</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0.2811358571052551</v>
+      </c>
+      <c r="M97" t="n">
+        <v>592.7110110102473</v>
+      </c>
+      <c r="N97" t="n">
+        <v>0.01651436282132847</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0.0128252545107081</v>
+      </c>
+      <c r="P97" t="n">
+        <v>3.144852704293019</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>1231.792379350805</v>
+      </c>
+      <c r="R97" t="n">
+        <v>17995.10758090019</v>
+      </c>
+      <c r="S97" t="n">
+        <v>-1.428574082242406e-06</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>1390000</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F98" t="n">
+        <v>3</v>
+      </c>
+      <c r="G98" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H98" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K98" t="n">
+        <v>-0.07883338944102042</v>
+      </c>
+      <c r="L98" t="n">
+        <v>-0.3333333432674408</v>
+      </c>
+      <c r="M98" t="n">
+        <v>870.4567054364321</v>
+      </c>
+      <c r="N98" t="n">
+        <v>0.01631993438058998</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0.001929302794763998</v>
+      </c>
+      <c r="P98" t="n">
+        <v>3.20141376351281</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>1192.01236657929</v>
+      </c>
+      <c r="R98" t="n">
+        <v>17995.24698853493</v>
+      </c>
+      <c r="S98" t="n">
+        <v>-4.380789521324519e-06</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>1430000</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F99" t="n">
+        <v>3</v>
+      </c>
+      <c r="G99" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H99" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K99" t="n">
+        <v>-0.02434575005427941</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0.08223105221986771</v>
+      </c>
+      <c r="M99" t="n">
+        <v>579.1464757319097</v>
+      </c>
+      <c r="N99" t="n">
+        <v>0.01729377797012454</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0.01597289057308308</v>
+      </c>
+      <c r="P99" t="n">
+        <v>3.132131950004951</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>1236.380264047476</v>
+      </c>
+      <c r="R99" t="n">
+        <v>17995.27404236794</v>
+      </c>
+      <c r="S99" t="n">
+        <v>-1.352896877088949e-06</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F100" t="n">
+        <v>3</v>
+      </c>
+      <c r="G100" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H100" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K100" t="n">
+        <v>-0.03620652207665934</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0.01496110949665308</v>
+      </c>
+      <c r="M100" t="n">
+        <v>590.4395233154297</v>
+      </c>
+      <c r="N100" t="n">
+        <v>0.01671852565680941</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0.01002312020282261</v>
+      </c>
+      <c r="P100" t="n">
+        <v>3.149185457596412</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>1229.783819580078</v>
+      </c>
+      <c r="R100" t="n">
+        <v>17995.21188950539</v>
+      </c>
+      <c r="S100" t="n">
+        <v>-2.012008655356517e-06</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>1350000</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F101" t="n">
+        <v>3</v>
+      </c>
+      <c r="G101" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H101" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K101" t="n">
+        <v>-0.04942076806077364</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" t="n">
+        <v>887.4874545393319</v>
+      </c>
+      <c r="N101" t="n">
+        <v>0.01663172764898236</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0.001582029381449617</v>
+      </c>
+      <c r="P101" t="n">
+        <v>3.200474265526081</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>1209.724936523437</v>
+      </c>
+      <c r="R101" t="n">
+        <v>17995.1273624897</v>
+      </c>
+      <c r="S101" t="n">
+        <v>-2.746341666010641e-06</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>1430000</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F102" t="n">
+        <v>3</v>
+      </c>
+      <c r="G102" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H102" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K102" t="n">
+        <v>-0.08014223270095441</v>
+      </c>
+      <c r="L102" t="n">
+        <v>-0.3906095325946808</v>
+      </c>
+      <c r="M102" t="n">
+        <v>701.3768676544403</v>
+      </c>
+      <c r="N102" t="n">
+        <v>0.01625454445272239</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0.005059287354259738</v>
+      </c>
+      <c r="P102" t="n">
+        <v>3.165900265420234</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>1235.917262221828</v>
+      </c>
+      <c r="R102" t="n">
+        <v>17995.37286758423</v>
+      </c>
+      <c r="S102" t="n">
+        <v>-4.453491088551867e-06</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>1460000</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F103" t="n">
+        <v>3</v>
+      </c>
+      <c r="G103" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H103" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K103" t="n">
+        <v>-0.05524620515414377</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0.2569428682327271</v>
+      </c>
+      <c r="M103" t="n">
+        <v>819.8634120993419</v>
+      </c>
+      <c r="N103" t="n">
+        <v>0.0168513578691465</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0.002833413760734348</v>
+      </c>
+      <c r="P103" t="n">
+        <v>3.161170484268502</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>1203.888327079907</v>
+      </c>
+      <c r="R103" t="n">
+        <v>17995.20490098</v>
+      </c>
+      <c r="S103" t="n">
+        <v>-3.070051464161718e-06</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>1410000</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F104" t="n">
+        <v>3</v>
+      </c>
+      <c r="G104" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H104" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K104" t="n">
+        <v>-0.09613056020177108</v>
+      </c>
+      <c r="L104" t="n">
+        <v>0.07192973047494888</v>
+      </c>
+      <c r="M104" t="n">
+        <v>731.7662897853986</v>
+      </c>
+      <c r="N104" t="n">
+        <v>0.01683706698509363</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0.004989312214400763</v>
+      </c>
+      <c r="P104" t="n">
+        <v>3.174919216345388</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>1200.675626565482</v>
+      </c>
+      <c r="R104" t="n">
+        <v>17995.07943463326</v>
+      </c>
+      <c r="S104" t="n">
+        <v>-5.342047005180683e-06</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F105" t="n">
+        <v>3</v>
+      </c>
+      <c r="G105" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H105" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K105" t="n">
+        <v>-0.03773985620417599</v>
+      </c>
+      <c r="L105" t="n">
+        <v>-0.09986966103315353</v>
+      </c>
+      <c r="M105" t="n">
+        <v>506.9271321977888</v>
+      </c>
+      <c r="N105" t="n">
+        <v>0.01651702901687134</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0.01510664714646048</v>
+      </c>
+      <c r="P105" t="n">
+        <v>3.088373894350869</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>1223.782485388275</v>
+      </c>
+      <c r="R105" t="n">
+        <v>17995.10270524025</v>
+      </c>
+      <c r="S105" t="n">
+        <v>-2.097229275228643e-06</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>1440000</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F106" t="n">
+        <v>3</v>
+      </c>
+      <c r="G106" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H106" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K106" t="n">
+        <v>-0.0652640527369429</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" t="n">
+        <v>862.8287138220383</v>
+      </c>
+      <c r="N106" t="n">
+        <v>0.01655374827391621</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0.002116386493443783</v>
+      </c>
+      <c r="P106" t="n">
+        <v>3.18383750360306</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>1196.9507724799</v>
+      </c>
+      <c r="R106" t="n">
+        <v>17995.2230796814</v>
+      </c>
+      <c r="S106" t="n">
+        <v>-3.626743188898461e-06</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>1470000</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F107" t="n">
+        <v>3</v>
+      </c>
+      <c r="G107" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H107" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K107" t="n">
+        <v>-0.08814059558235818</v>
+      </c>
+      <c r="L107" t="n">
+        <v>-0.1576727330684662</v>
+      </c>
+      <c r="M107" t="n">
+        <v>851.469203819223</v>
+      </c>
+      <c r="N107" t="n">
+        <v>0.01603374391903772</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0.002235823491740602</v>
+      </c>
+      <c r="P107" t="n">
+        <v>3.18215003629931</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>1206.03878433978</v>
+      </c>
+      <c r="R107" t="n">
+        <v>17995.15147709846</v>
+      </c>
+      <c r="S107" t="n">
+        <v>-4.898019096673364e-06</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>1530000</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F108" t="n">
+        <v>3</v>
+      </c>
+      <c r="G108" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H108" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K108" t="n">
+        <v>-0.06071021228608397</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" t="n">
+        <v>887.1452327579647</v>
+      </c>
+      <c r="N108" t="n">
+        <v>0.01688449598953758</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0.001778534818208434</v>
+      </c>
+      <c r="P108" t="n">
+        <v>3.185303858348302</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>1203.266598405509</v>
+      </c>
+      <c r="R108" t="n">
+        <v>17995.40895986557</v>
+      </c>
+      <c r="S108" t="n">
+        <v>-3.373650047158333e-06</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>1460000</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F109" t="n">
+        <v>3</v>
+      </c>
+      <c r="G109" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H109" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K109" t="n">
+        <v>-0.07936706730654569</v>
+      </c>
+      <c r="L109" t="n">
+        <v>-0.2594461441040039</v>
+      </c>
+      <c r="M109" t="n">
+        <v>796.2067766581496</v>
+      </c>
+      <c r="N109" t="n">
+        <v>0.0168999309665454</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0.003198579924241701</v>
+      </c>
+      <c r="P109" t="n">
+        <v>3.174377723915936</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>1210.38081036867</v>
+      </c>
+      <c r="R109" t="n">
+        <v>17995.137134552</v>
+      </c>
+      <c r="S109" t="n">
+        <v>-4.410473046863034e-06</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>1440000</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="F110" t="n">
+        <v>3</v>
+      </c>
+      <c r="G110" t="n">
+        <v>4096</v>
+      </c>
+      <c r="H110" t="n">
+        <v>40960</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K110" t="n">
+        <v>-0.06132579872300366</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" t="n">
+        <v>863.6765763907597</v>
+      </c>
+      <c r="N110" t="n">
+        <v>0.01177540016086663</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0.001968398201450541</v>
+      </c>
+      <c r="P110" t="n">
+        <v>3.260947574418167</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>1195.962221239434</v>
+      </c>
+      <c r="R110" t="n">
+        <v>17995.25778579712</v>
+      </c>
+      <c r="S110" t="n">
+        <v>-3.407886647303573e-06</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>1440000</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="F111" t="n">
+        <v>3</v>
+      </c>
+      <c r="G111" t="n">
+        <v>4096</v>
+      </c>
+      <c r="H111" t="n">
+        <v>40960</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K111" t="n">
+        <v>-0.11276245245689</v>
+      </c>
+      <c r="L111" t="n">
+        <v>-0.2458153814077377</v>
+      </c>
+      <c r="M111" t="n">
+        <v>835.1176486545139</v>
+      </c>
+      <c r="N111" t="n">
+        <v>0.01234778816647389</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0.002459326849716222</v>
+      </c>
+      <c r="P111" t="n">
+        <v>3.276864109767808</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>1192.642179299857</v>
+      </c>
+      <c r="R111" t="n">
+        <v>17995.14132499695</v>
+      </c>
+      <c r="S111" t="n">
+        <v>-6.2662721242568e-06</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>1460000</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="F112" t="n">
+        <v>3</v>
+      </c>
+      <c r="G112" t="n">
+        <v>4096</v>
+      </c>
+      <c r="H112" t="n">
+        <v>40960</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K112" t="n">
+        <v>-0.0949512809381042</v>
+      </c>
+      <c r="L112" t="n">
+        <v>-0.1670000106096268</v>
+      </c>
+      <c r="M112" t="n">
+        <v>860.9135980475439</v>
+      </c>
+      <c r="N112" t="n">
+        <v>0.01172476519337472</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0.002087705283830634</v>
+      </c>
+      <c r="P112" t="n">
+        <v>3.259470003924958</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>1187.889831542969</v>
+      </c>
+      <c r="R112" t="n">
+        <v>17995.33067846298</v>
+      </c>
+      <c r="S112" t="n">
+        <v>-5.276439907366803e-06</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>1450000</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="F113" t="n">
+        <v>3</v>
+      </c>
+      <c r="G113" t="n">
+        <v>4096</v>
+      </c>
+      <c r="H113" t="n">
+        <v>40960</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K113" t="n">
+        <v>-0.08317331224042054</v>
+      </c>
+      <c r="L113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" t="n">
+        <v>843.7235316446382</v>
+      </c>
+      <c r="N113" t="n">
+        <v>0.01200351316262694</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0.002318393690717023</v>
+      </c>
+      <c r="P113" t="n">
+        <v>3.269369883080051</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>1192.302540779114</v>
+      </c>
+      <c r="R113" t="n">
+        <v>17995.10228347778</v>
+      </c>
+      <c r="S113" t="n">
+        <v>-4.621997192913218e-06</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>1430000</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="F114" t="n">
+        <v>3</v>
+      </c>
+      <c r="G114" t="n">
+        <v>4096</v>
+      </c>
+      <c r="H114" t="n">
+        <v>40960</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K114" t="n">
+        <v>-0.08441317701790403</v>
+      </c>
+      <c r="L114" t="n">
+        <v>-0.2727272808551788</v>
+      </c>
+      <c r="M114" t="n">
+        <v>846.4230077783544</v>
+      </c>
+      <c r="N114" t="n">
+        <v>0.01207046229940127</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0.002249463367180022</v>
+      </c>
+      <c r="P114" t="n">
+        <v>3.27051186895037</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>1188.534644150152</v>
+      </c>
+      <c r="R114" t="n">
+        <v>17995.28890514374</v>
+      </c>
+      <c r="S114" t="n">
+        <v>-4.6908486694968e-06</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>1460000</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="F115" t="n">
+        <v>3</v>
+      </c>
+      <c r="G115" t="n">
+        <v>4096</v>
+      </c>
+      <c r="H115" t="n">
+        <v>40960</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K115" t="n">
+        <v>-0.06385532422916172</v>
+      </c>
+      <c r="L115" t="n">
+        <v>0.07402666658163071</v>
+      </c>
+      <c r="M115" t="n">
+        <v>824.4864073452884</v>
+      </c>
+      <c r="N115" t="n">
+        <v>0.01130786305293441</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0.002419316042077673</v>
+      </c>
+      <c r="P115" t="n">
+        <v>3.265386674502125</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>1201.28309410037</v>
+      </c>
+      <c r="R115" t="n">
+        <v>17995.03974938393</v>
+      </c>
+      <c r="S115" t="n">
+        <v>-3.548495869888137e-06</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>1390000</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="F116" t="n">
+        <v>3</v>
+      </c>
+      <c r="G116" t="n">
+        <v>4096</v>
+      </c>
+      <c r="H116" t="n">
+        <v>40960</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K116" t="n">
+        <v>-0.0959108655856882</v>
+      </c>
+      <c r="L116" t="n">
+        <v>-0.1528666615486145</v>
+      </c>
+      <c r="M116" t="n">
+        <v>842.0181998932104</v>
+      </c>
+      <c r="N116" t="n">
+        <v>0.01187816835149671</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0.002442295549289239</v>
+      </c>
+      <c r="P116" t="n">
+        <v>3.25810300703529</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>1198.868823026134</v>
+      </c>
+      <c r="R116" t="n">
+        <v>17995.1874063015</v>
+      </c>
+      <c r="S116" t="n">
+        <v>-5.329806432140987e-06</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>1440000</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="F117" t="n">
+        <v>3</v>
+      </c>
+      <c r="G117" t="n">
+        <v>4096</v>
+      </c>
+      <c r="H117" t="n">
+        <v>40960</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K117" t="n">
+        <v>-0.07779921093565968</v>
+      </c>
+      <c r="L117" t="n">
+        <v>-0.1063666716217995</v>
+      </c>
+      <c r="M117" t="n">
+        <v>875.3113945855034</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.0120144174023367</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.001776625151465209</v>
+      </c>
+      <c r="P117" t="n">
+        <v>3.259148041407267</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>1194.489860733696</v>
+      </c>
+      <c r="R117" t="n">
+        <v>17995.21722435951</v>
+      </c>
+      <c r="S117" t="n">
+        <v>-4.323327135520517e-06</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>1440000</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="F118" t="n">
+        <v>3</v>
+      </c>
+      <c r="G118" t="n">
+        <v>4096</v>
+      </c>
+      <c r="H118" t="n">
+        <v>40960</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K118" t="n">
+        <v>-0.07233081254849417</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.2545230686664581</v>
+      </c>
+      <c r="M118" t="n">
+        <v>887.4151823255751</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.01159866478787187</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.001654869293013369</v>
+      </c>
+      <c r="P118" t="n">
+        <v>3.26870101193587</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>1197.735852162772</v>
+      </c>
+      <c r="R118" t="n">
+        <v>17995.05531740189</v>
+      </c>
+      <c r="S118" t="n">
+        <v>-4.019482645243529e-06</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>1510000</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F119" t="n">
+        <v>3</v>
+      </c>
+      <c r="G119" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H119" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K119" t="n">
+        <v>-0.04788498248710661</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.1359096765518188</v>
+      </c>
+      <c r="M119" t="n">
+        <v>677.1191933739265</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.01648473142247115</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.008031070349534274</v>
+      </c>
+      <c r="P119" t="n">
+        <v>3.173563033539728</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>1215.133023742243</v>
+      </c>
+      <c r="R119" t="n">
+        <v>17995.34566259384</v>
+      </c>
+      <c r="S119" t="n">
+        <v>-2.660964861966674e-06</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>1460000</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="F120" t="n">
+        <v>3</v>
+      </c>
+      <c r="G120" t="n">
+        <v>4096</v>
+      </c>
+      <c r="H120" t="n">
+        <v>40960</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K120" t="n">
+        <v>-0.0549575405535033</v>
+      </c>
+      <c r="L120" t="n">
+        <v>-0.1418285667896271</v>
+      </c>
+      <c r="M120" t="n">
+        <v>885.5548400878906</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.01181424737853162</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.001604778013536227</v>
+      </c>
+      <c r="P120" t="n">
+        <v>3.255590641335265</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>1198.729158528646</v>
+      </c>
+      <c r="R120" t="n">
+        <v>17995.14831590652</v>
+      </c>
+      <c r="S120" t="n">
+        <v>-3.054019871840926e-06</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>1450000</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="F121" t="n">
+        <v>3</v>
+      </c>
+      <c r="G121" t="n">
+        <v>4096</v>
+      </c>
+      <c r="H121" t="n">
+        <v>40960</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K121" t="n">
+        <v>-0.07434720144896158</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.1072727218270302</v>
+      </c>
+      <c r="M121" t="n">
+        <v>829.040234585466</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.01203147053499432</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.002522198659682865</v>
+      </c>
+      <c r="P121" t="n">
+        <v>3.262015653478688</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>1197.161431312561</v>
+      </c>
+      <c r="R121" t="n">
+        <v>17995.32396507263</v>
+      </c>
+      <c r="S121" t="n">
+        <v>-4.13147335348133e-06</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>620000</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="F122" t="n">
+        <v>3</v>
+      </c>
+      <c r="G122" t="n">
+        <v>4096</v>
+      </c>
+      <c r="H122" t="n">
+        <v>40960</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K122" t="n">
+        <v>-0.1016146971603795</v>
+      </c>
+      <c r="L122" t="n">
+        <v>-0.3333333432674408</v>
+      </c>
+      <c r="M122" t="n">
+        <v>832.1159057617188</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.01239575033209154</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.002598191141649814</v>
+      </c>
+      <c r="P122" t="n">
+        <v>3.286209517909635</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>1198.667122676455</v>
+      </c>
+      <c r="R122" t="n">
+        <v>7716.180715084076</v>
+      </c>
+      <c r="S122" t="n">
+        <v>-1.316904060602634e-05</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>1410000</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F123" t="n">
+        <v>3</v>
+      </c>
+      <c r="G123" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H123" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.001199247682110426</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.1090409904718399</v>
+      </c>
+      <c r="M123" t="n">
+        <v>337.1761070413792</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.01675939448733828</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.03749355806885704</v>
+      </c>
+      <c r="P123" t="n">
+        <v>2.970382238956208</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>1283.899369834126</v>
+      </c>
+      <c r="R123" t="n">
+        <v>17995.32497596741</v>
+      </c>
+      <c r="S123" t="n">
+        <v>6.664217977235814e-08</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>1390000</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F124" t="n">
+        <v>3</v>
+      </c>
+      <c r="G124" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H124" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K124" t="n">
+        <v>-0.04421959941744247</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" t="n">
+        <v>914.5937541520515</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.01659754093955545</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.001261366287356037</v>
+      </c>
+      <c r="P124" t="n">
+        <v>3.163660133777022</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>1202.332063605986</v>
+      </c>
+      <c r="R124" t="n">
+        <v>17995.28908824921</v>
+      </c>
+      <c r="S124" t="n">
+        <v>-2.45728752678486e-06</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>1460000</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F125" t="n">
+        <v>3</v>
+      </c>
+      <c r="G125" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H125" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K125" t="n">
+        <v>-0.05507403257664065</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" t="n">
+        <v>911.8510148444143</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.01717650823240333</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.001386294469353938</v>
+      </c>
+      <c r="P125" t="n">
+        <v>3.107072212258164</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>1203.592844801683</v>
+      </c>
+      <c r="R125" t="n">
+        <v>17995.29445552826</v>
+      </c>
+      <c r="S125" t="n">
+        <v>-3.060468541525954e-06</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>1410000</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F126" t="n">
+        <v>3</v>
+      </c>
+      <c r="G126" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H126" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K126" t="n">
+        <v>-0.05135973393157495</v>
+      </c>
+      <c r="L126" t="n">
+        <v>-0.1486631631851196</v>
+      </c>
+      <c r="M126" t="n">
+        <v>549.2495457534249</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.01637312975909674</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.01243788041624198</v>
+      </c>
+      <c r="P126" t="n">
+        <v>3.144995479719013</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>1216.890735486998</v>
+      </c>
+      <c r="R126" t="n">
+        <v>17995.24465966225</v>
+      </c>
+      <c r="S126" t="n">
+        <v>-2.854072556551666e-06</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>730000</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F127" t="n">
+        <v>3</v>
+      </c>
+      <c r="G127" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H127" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K127" t="n">
+        <v>-0.06820672389900161</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.2575692236423492</v>
+      </c>
+      <c r="M127" t="n">
+        <v>800.8920229559076</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.0161217793427182</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.002628139609524541</v>
+      </c>
+      <c r="P127" t="n">
+        <v>3.186326604999908</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>1196.436011529738</v>
+      </c>
+      <c r="R127" t="n">
+        <v>8963.350725412369</v>
+      </c>
+      <c r="S127" t="n">
+        <v>-7.609511887739245e-06</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>1490000</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F128" t="n">
+        <v>3</v>
+      </c>
+      <c r="G128" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H128" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.002493537762030434</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.114839218556881</v>
+      </c>
+      <c r="M128" t="n">
+        <v>420.8207481435481</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.01691453896043166</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.02421984370817548</v>
+      </c>
+      <c r="P128" t="n">
+        <v>3.026945294949833</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>1256.645556806707</v>
+      </c>
+      <c r="R128" t="n">
+        <v>17995.35598397255</v>
+      </c>
+      <c r="S128" t="n">
+        <v>1.385656257231748e-07</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>490000</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F129" t="n">
+        <v>3</v>
+      </c>
+      <c r="G129" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H129" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K129" t="n">
+        <v>-0.06841414215043187</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" t="n">
+        <v>880.0150500488281</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.01623516849687566</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.001893224955141625</v>
+      </c>
+      <c r="P129" t="n">
+        <v>3.226646943092346</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>1195.927143818623</v>
+      </c>
+      <c r="R129" t="n">
+        <v>6123.907691001892</v>
+      </c>
+      <c r="S129" t="n">
+        <v>-1.117164817016357e-05</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>500000</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F130" t="n">
+        <v>3</v>
+      </c>
+      <c r="G130" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H130" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K130" t="n">
+        <v>-0.1194992702640593</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.1464749872684479</v>
+      </c>
+      <c r="M130" t="n">
+        <v>804.2698315429687</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.01724985990997242</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.003048165973387254</v>
+      </c>
+      <c r="P130" t="n">
+        <v>3.235065455436707</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>1192.510180664063</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6068.017175197601</v>
+      </c>
+      <c r="S130" t="n">
+        <v>-1.969329796107043e-05</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>1520000</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F131" t="n">
+        <v>3</v>
+      </c>
+      <c r="G131" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H131" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K131" t="n">
+        <v>-0.05202118511078879</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.11036666482687</v>
+      </c>
+      <c r="M131" t="n">
+        <v>861.9531904521741</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.01700959076554003</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.001993581213560312</v>
+      </c>
+      <c r="P131" t="n">
+        <v>3.182149005563636</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>1208.285491943359</v>
+      </c>
+      <c r="R131" t="n">
+        <v>17995.34384942055</v>
+      </c>
+      <c r="S131" t="n">
+        <v>-2.890813620794686e-06</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>1480000</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F132" t="n">
+        <v>3</v>
+      </c>
+      <c r="G132" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H132" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K132" t="n">
+        <v>-0.05582696905774946</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.2473333328962326</v>
+      </c>
+      <c r="M132" t="n">
+        <v>504.455322214075</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.01687058000622884</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.01488119825228131</v>
+      </c>
+      <c r="P132" t="n">
+        <v>3.119919672205641</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>1216.859041621767</v>
+      </c>
+      <c r="R132" t="n">
+        <v>17995.34313344955</v>
+      </c>
+      <c r="S132" t="n">
+        <v>-3.102300892166867e-06</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F133" t="n">
+        <v>3</v>
+      </c>
+      <c r="G133" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H133" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K133" t="n">
+        <v>-0.0695333406329155</v>
+      </c>
+      <c r="L133" t="n">
+        <v>-0.0695333406329155</v>
+      </c>
+      <c r="M133" t="n">
+        <v>808.4285888671875</v>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P133" t="n">
+        <v>3.295706033706665</v>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R133" t="n">
+        <v>130.4621279239655</v>
+      </c>
+      <c r="S133" t="n">
+        <v>-0.0005329772075574313</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F134" t="n">
+        <v>3</v>
+      </c>
+      <c r="G134" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H134" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K134" t="n">
+        <v>-0.197160005569458</v>
+      </c>
+      <c r="L134" t="n">
+        <v>-0.197160005569458</v>
+      </c>
+      <c r="M134" t="n">
+        <v>959.6666870117188</v>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P134" t="n">
+        <v>3.295767307281494</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>1199.5029296875</v>
+      </c>
+      <c r="R134" t="n">
+        <v>130.5646452903748</v>
+      </c>
+      <c r="S134" t="n">
+        <v>-0.001510056609359874</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>SoccerTwos</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>poca</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>1510000</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F135" t="n">
+        <v>3</v>
+      </c>
+      <c r="G135" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H135" t="n">
+        <v>20480</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.00568028065431493</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.1287574023008347</v>
+      </c>
+      <c r="M135" t="n">
+        <v>382.2769290595655</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.01681859429243585</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.02994660052948821</v>
+      </c>
+      <c r="P135" t="n">
+        <v>3.01849955280885</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>1267.88139851888</v>
+      </c>
+      <c r="R135" t="n">
+        <v>17995.28589963913</v>
+      </c>
+      <c r="S135" t="n">
+        <v>3.156538154489027e-07</v>
       </c>
     </row>
   </sheetData>
